--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD941738-DAD7-4226-93B9-610D4612DB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12D9B8F-7B76-40AB-BE29-6D0A7D1B2BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="105" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7065" yWindow="675" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>Name</t>
   </si>
@@ -205,6 +205,29 @@
   </si>
   <si>
     <t>float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Enemy/Enemy_Prefab/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Police</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_Prefab</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -972,6 +995,9 @@
         <v>27</v>
       </c>
       <c r="C7" s="4"/>
+      <c r="E7" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="F7" s="12" t="s">
         <v>18</v>
       </c>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12D9B8F-7B76-40AB-BE29-6D0A7D1B2BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E31053E-A859-4AD6-BCA4-46F2F9ED4245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7065" yWindow="675" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="105" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
   <si>
     <t>Name</t>
   </si>
@@ -225,8 +225,39 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>_Prefab</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>loat</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ttackCoolDown</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -813,7 +844,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:K1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
@@ -827,7 +858,7 @@
     <col min="11" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -845,7 +876,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="12.75">
+    <row r="2" spans="1:11" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -876,8 +907,11 @@
       <c r="J2" s="15" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <c r="K2" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="11" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -908,8 +942,11 @@
       <c r="J3" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K3" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
@@ -938,8 +975,11 @@
       <c r="J4" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
@@ -962,8 +1002,11 @@
       <c r="J5" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
@@ -986,8 +1029,11 @@
       <c r="J6" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>24</v>
       </c>
@@ -1013,8 +1059,11 @@
       <c r="J7" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K7" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>25</v>
       </c>
@@ -1037,8 +1086,11 @@
       <c r="J8" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K8" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>26</v>
       </c>
@@ -1061,8 +1113,11 @@
       <c r="J9" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K9" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>31</v>
       </c>
@@ -1085,8 +1140,11 @@
       <c r="J10" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -1109,8 +1167,11 @@
       <c r="J11" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -1133,23 +1194,26 @@
       <c r="J12" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+    <row r="14" spans="1:11" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+    <row r="15" spans="1:11" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+    <row r="16" spans="1:11" ht="15.75" customHeight="1">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E31053E-A859-4AD6-BCA4-46F2F9ED4245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1150A0B-9158-46B5-98AB-4D7528D4689E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4740" yWindow="105" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
   <si>
     <t>Name</t>
   </si>
@@ -258,6 +258,29 @@
         <family val="2"/>
       </rPr>
       <t>ttackCoolDown</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Enemy/Enemy_Prefab/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Athlete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_Prefab</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1125,6 +1148,9 @@
         <v>30</v>
       </c>
       <c r="C10" s="1"/>
+      <c r="E10" s="15" t="s">
+        <v>43</v>
+      </c>
       <c r="F10" s="12" t="s">
         <v>18</v>
       </c>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1150A0B-9158-46B5-98AB-4D7528D4689E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9771FA47-65D0-4EDD-87C2-D9BC686E5FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="105" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8760" yWindow="1155" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>Name</t>
   </si>
@@ -134,62 +134,24 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>enemy_citizen_02</t>
-  </si>
-  <si>
-    <t>enemy_citizen_03</t>
-  </si>
-  <si>
     <t>시민1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>시민2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>시민3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>enemy_police_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>enemy_police_02</t>
-  </si>
-  <si>
-    <t>enemy_police_03</t>
-  </si>
-  <si>
     <t>경찰1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>경찰2</t>
-  </si>
-  <si>
-    <t>경찰3</t>
-  </si>
-  <si>
     <t>운동선수1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>enemy_athlete_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemy_athlete_02</t>
-  </si>
-  <si>
-    <t>enemy_athlete_03</t>
-  </si>
-  <si>
-    <t>운동선수2</t>
-  </si>
-  <si>
-    <t>운동선수3</t>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Icon/Citizen_Icon</t>
@@ -279,9 +241,38 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>_Prefab</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_soldiergun_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>군인(총)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/SoldierGun_Prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_soldierknife_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>군인(칼)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/SoldierKnife_Prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -424,7 +415,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -432,9 +423,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -867,14 +855,14 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K1000"/>
+  <dimension ref="A1:K996"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
     <col min="3" max="3" width="68.140625" style="3" customWidth="1"/>
     <col min="4" max="4" width="34.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="37.28515625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="44.42578125" style="3" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="3" customWidth="1"/>
     <col min="7" max="9" width="12.5703125" style="3"/>
     <col min="10" max="10" width="15.85546875" style="3" customWidth="1"/>
@@ -895,7 +883,7 @@
       <c r="E1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>17</v>
       </c>
     </row>
@@ -916,57 +904,57 @@
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="13" t="s">
-        <v>42</v>
+      <c r="K3" s="12" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1">
@@ -974,16 +962,16 @@
         <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="12" t="s">
+      <c r="D4" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="3">
@@ -1004,270 +992,188 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="E5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="3">
+        <v>15</v>
+      </c>
+      <c r="H5" s="3">
+        <v>20</v>
+      </c>
+      <c r="I5" s="3">
+        <v>4</v>
+      </c>
+      <c r="J5" s="3">
+        <v>5</v>
+      </c>
+      <c r="K5" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="F5" s="12" t="s">
+      <c r="C6" s="1"/>
+      <c r="E6" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="3">
-        <v>5</v>
-      </c>
-      <c r="H5" s="3">
+      <c r="G6" s="3">
         <v>10</v>
       </c>
-      <c r="I5" s="3">
-        <v>2</v>
-      </c>
-      <c r="J5" s="3">
+      <c r="H6" s="3">
+        <v>15</v>
+      </c>
+      <c r="I6" s="3">
+        <v>3</v>
+      </c>
+      <c r="J6" s="3">
+        <v>3</v>
+      </c>
+      <c r="K6" s="3">
         <v>1</v>
       </c>
-      <c r="K5" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="F6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="3">
-        <v>5</v>
-      </c>
-      <c r="H6" s="3">
-        <v>10</v>
-      </c>
-      <c r="I6" s="3">
-        <v>2</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3">
-        <v>2</v>
-      </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="E7" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>18</v>
+      <c r="A7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="E7" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="G7" s="3">
+        <v>50</v>
+      </c>
+      <c r="H7" s="3">
+        <v>80</v>
+      </c>
+      <c r="I7" s="3">
+        <v>3</v>
+      </c>
+      <c r="J7" s="3">
         <v>15</v>
       </c>
-      <c r="H7" s="3">
-        <v>20</v>
-      </c>
-      <c r="I7" s="3">
+      <c r="K7" s="3">
         <v>4</v>
       </c>
-      <c r="J7" s="3">
-        <v>5</v>
-      </c>
-      <c r="K7" s="3">
-        <v>5</v>
-      </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="F8" s="12" t="s">
-        <v>18</v>
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="E8" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="G8" s="3">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="H8" s="3">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I8" s="3">
         <v>4</v>
       </c>
       <c r="J8" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K8" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="F9" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="3">
-        <v>15</v>
-      </c>
-      <c r="H9" s="3">
-        <v>20</v>
-      </c>
-      <c r="I9" s="3">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3">
-        <v>5</v>
-      </c>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="E10" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="3">
-        <v>10</v>
-      </c>
-      <c r="H10" s="3">
-        <v>15</v>
-      </c>
-      <c r="I10" s="3">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1</v>
-      </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="F11" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="3">
-        <v>10</v>
-      </c>
-      <c r="H11" s="3">
-        <v>15</v>
-      </c>
-      <c r="I11" s="3">
-        <v>3</v>
-      </c>
-      <c r="J11" s="3">
-        <v>3</v>
-      </c>
-      <c r="K11" s="3">
-        <v>1</v>
-      </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
       <c r="C12" s="6"/>
-      <c r="F12" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="3">
-        <v>10</v>
-      </c>
-      <c r="H12" s="3">
-        <v>15</v>
-      </c>
-      <c r="I12" s="3">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1</v>
-      </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
       <c r="A22" s="7"/>
@@ -1290,14 +1196,14 @@
       <c r="C25" s="7"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
@@ -1319,39 +1225,23 @@
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
     </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -2300,10 +2190,6 @@
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9771FA47-65D0-4EDD-87C2-D9BC686E5FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE584D12-99FD-40E4-85C9-7DF02B68BCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8760" yWindow="1155" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15765" yWindow="120" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
     <t>Name</t>
   </si>
@@ -273,6 +273,57 @@
   </si>
   <si>
     <t>Rare</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_tank_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_firetank_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_drill_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>탱크</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염탱크</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>드릴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Tank_Prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/FireTank_Prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Drill_Prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>pic</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1111,19 +1162,94 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
+      <c r="A9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="C9" s="4"/>
+      <c r="E9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="3">
+        <v>250</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>2</v>
+      </c>
+      <c r="J9" s="3">
+        <v>150</v>
+      </c>
+      <c r="K9" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="C10" s="1"/>
+      <c r="E10" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="3">
+        <v>200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
+        <v>280</v>
+      </c>
+      <c r="K10" s="3">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="C11" s="1"/>
+      <c r="E11" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="3">
+        <v>300</v>
+      </c>
+      <c r="H11" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3">
+        <v>450</v>
+      </c>
+      <c r="K11" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE584D12-99FD-40E4-85C9-7DF02B68BCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEED53A-C571-4CF9-BAEF-1A86770E9B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15765" yWindow="120" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10305" yWindow="135" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -1026,7 +1026,7 @@
         <v>18</v>
       </c>
       <c r="G4" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H4" s="3">
         <v>10</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEED53A-C571-4CF9-BAEF-1A86770E9B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AA3125-8AE5-4E0C-932D-9E3629CC6ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10305" yWindow="135" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="0" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
   <si>
     <t>Name</t>
   </si>
@@ -323,6 +323,81 @@
         <family val="2"/>
       </rPr>
       <t>pic</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">loat </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nt</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ropHealKitChance</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ropUmbraChance</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ropUmbraAmount</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -906,7 +981,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K996"/>
+  <dimension ref="A1:N996"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
@@ -917,10 +992,14 @@
     <col min="6" max="6" width="19.5703125" style="3" customWidth="1"/>
     <col min="7" max="9" width="12.5703125" style="3"/>
     <col min="10" max="10" width="15.85546875" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="12.5703125" style="3"/>
+    <col min="11" max="11" width="17" style="3" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="17.140625" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" customHeight="1">
+    <row r="1" spans="1:14" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -938,7 +1017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="12.75">
+    <row r="2" spans="1:14" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -972,8 +1051,17 @@
       <c r="K2" s="14" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <c r="L2" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -1007,8 +1095,17 @@
       <c r="K3" s="12" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" customHeight="1">
+      <c r="L3" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
@@ -1040,8 +1137,17 @@
       <c r="K4" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" customHeight="1">
+      <c r="L4" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="N4" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
@@ -1070,8 +1176,17 @@
       <c r="K5" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" customHeight="1">
+      <c r="L5" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="N5" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
@@ -1100,8 +1215,17 @@
       <c r="K6" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1">
+      <c r="L6" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="N6" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
@@ -1130,8 +1254,17 @@
       <c r="K7" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1">
+      <c r="L7" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="N7" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
@@ -1160,8 +1293,17 @@
       <c r="K8" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1">
+      <c r="L8" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="N8" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>39</v>
       </c>
@@ -1190,8 +1332,17 @@
       <c r="K9" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" customHeight="1">
+      <c r="L9" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="N9" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>40</v>
       </c>
@@ -1220,8 +1371,17 @@
       <c r="K10" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" customHeight="1">
+      <c r="L10" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="N10" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>41</v>
       </c>
@@ -1250,28 +1410,37 @@
       <c r="K11" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" customHeight="1">
+      <c r="L11" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="N11" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
     </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1">
+    <row r="13" spans="1:14" ht="15.75" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1">
+    <row r="14" spans="1:14" ht="15.75" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
     </row>
-    <row r="15" spans="1:11" ht="15.75" customHeight="1">
+    <row r="15" spans="1:14" ht="15.75" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
     </row>
-    <row r="16" spans="1:11" ht="15.75" customHeight="1">
+    <row r="16" spans="1:14" ht="15.75" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AA3125-8AE5-4E0C-932D-9E3629CC6ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86AB2C52-EB90-4EBA-8FE1-477CFE9C3BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="0" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6750" yWindow="690" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -1141,7 +1141,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M4" s="3">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="N4" s="3">
         <v>100</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86AB2C52-EB90-4EBA-8FE1-477CFE9C3BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A54448A-2350-4677-A544-4A8B2BD45E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6750" yWindow="690" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3975" yWindow="885" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
   <si>
     <t>Name</t>
   </si>
@@ -130,31 +130,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>normal</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>시민1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>enemy_police_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>경찰1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>운동선수1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>enemy_athlete_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Enemy/Enemy_Icon/Citizen_Icon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -272,10 +252,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Rare</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>enemy_tank_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -309,21 +285,6 @@
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Drill_Prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>pic</t>
-    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -399,6 +360,46 @@
       </rPr>
       <t>ropUmbraAmount</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>시민</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>경찰</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>운동선수</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instance</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectilePath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectileSpeed</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Projectile</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_Bullet</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_Shell</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -497,7 +498,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -524,14 +525,25 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -541,7 +553,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -561,12 +573,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -981,25 +997,27 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N996"/>
+  <dimension ref="A1:P996"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="68.140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="34.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="3" customWidth="1"/>
     <col min="5" max="5" width="44.42578125" style="3" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="3" customWidth="1"/>
-    <col min="7" max="9" width="12.5703125" style="3"/>
-    <col min="10" max="10" width="15.85546875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="17" style="3" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" style="3" customWidth="1"/>
-    <col min="14" max="14" width="17.140625" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="12.5703125" style="3"/>
+    <col min="7" max="7" width="51.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" style="3" customWidth="1"/>
+    <col min="9" max="11" width="12.5703125" style="3"/>
+    <col min="12" max="12" width="15.85546875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="17" style="3" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" customHeight="1">
+    <row r="1" spans="1:16" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1013,11 +1031,13 @@
       <c r="E1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="12.75">
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:16" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1033,35 +1053,41 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="M2" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="N2" s="14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <c r="F2" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -1077,370 +1103,398 @@
       <c r="E3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="J3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="K3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="L3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="15.75" customHeight="1">
+      <c r="M3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="D4" s="13"/>
+      <c r="E4" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="3">
+      <c r="F4" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="3">
+        <v>20</v>
+      </c>
+      <c r="J4" s="3">
         <v>10</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2</v>
-      </c>
-      <c r="J4" s="3">
-        <v>1</v>
       </c>
       <c r="K4" s="3">
         <v>2</v>
       </c>
       <c r="L4" s="3">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3">
+        <v>2</v>
+      </c>
+      <c r="N4" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="M4" s="3">
+      <c r="O4" s="3">
         <v>1</v>
       </c>
-      <c r="N4" s="3">
+      <c r="P4" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15.75" customHeight="1">
+    <row r="5" spans="1:16" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="E5" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="3">
+        <v>15</v>
+      </c>
+      <c r="J5" s="3">
         <v>20</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="E5" s="14" t="s">
+      <c r="K5" s="3">
+        <v>4</v>
+      </c>
+      <c r="L5" s="3">
+        <v>5</v>
+      </c>
+      <c r="M5" s="3">
+        <v>5</v>
+      </c>
+      <c r="N5" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="P5" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="E6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="3">
+        <v>10</v>
+      </c>
+      <c r="J6" s="3">
+        <v>15</v>
+      </c>
+      <c r="K6" s="3">
+        <v>3</v>
+      </c>
+      <c r="L6" s="3">
+        <v>3</v>
+      </c>
+      <c r="M6" s="3">
+        <v>1</v>
+      </c>
+      <c r="N6" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="P6" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="C7" s="1"/>
+      <c r="E7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="4">
+        <v>7</v>
+      </c>
+      <c r="I7" s="3">
+        <v>50</v>
+      </c>
+      <c r="J7" s="3">
+        <v>80</v>
+      </c>
+      <c r="K7" s="3">
+        <v>3</v>
+      </c>
+      <c r="L7" s="3">
         <v>15</v>
       </c>
-      <c r="H5" s="3">
-        <v>20</v>
-      </c>
-      <c r="I5" s="3">
+      <c r="M7" s="3">
         <v>4</v>
       </c>
-      <c r="J5" s="3">
+      <c r="N7" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="P7" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="E8" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="3">
+        <v>50</v>
+      </c>
+      <c r="J8" s="3">
+        <v>100</v>
+      </c>
+      <c r="K8" s="3">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3">
+        <v>30</v>
+      </c>
+      <c r="M8" s="3">
+        <v>2</v>
+      </c>
+      <c r="N8" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="P8" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="E9" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="4">
         <v>5</v>
       </c>
-      <c r="K5" s="3">
+      <c r="I9" s="3">
+        <v>250</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K9" s="3">
+        <v>2</v>
+      </c>
+      <c r="L9" s="3">
+        <v>150</v>
+      </c>
+      <c r="M9" s="3">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="P9" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="E10" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="3">
+        <v>200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K10" s="3">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3">
+        <v>280</v>
+      </c>
+      <c r="M10" s="3">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="P10" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="E11" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="3">
+        <v>300</v>
+      </c>
+      <c r="J11" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K11" s="3">
+        <v>1</v>
+      </c>
+      <c r="L11" s="3">
+        <v>450</v>
+      </c>
+      <c r="M11" s="3">
         <v>5</v>
       </c>
-      <c r="L5" s="3">
+      <c r="N11" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="M5" s="3">
+      <c r="O11" s="3">
         <v>0.05</v>
       </c>
-      <c r="N5" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="E6" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="3">
-        <v>10</v>
-      </c>
-      <c r="H6" s="3">
-        <v>15</v>
-      </c>
-      <c r="I6" s="3">
-        <v>3</v>
-      </c>
-      <c r="J6" s="3">
-        <v>3</v>
-      </c>
-      <c r="K6" s="3">
-        <v>1</v>
-      </c>
-      <c r="L6" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="N6" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="E7" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="3">
-        <v>50</v>
-      </c>
-      <c r="H7" s="3">
-        <v>80</v>
-      </c>
-      <c r="I7" s="3">
-        <v>3</v>
-      </c>
-      <c r="J7" s="3">
-        <v>15</v>
-      </c>
-      <c r="K7" s="3">
-        <v>4</v>
-      </c>
-      <c r="L7" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="N7" s="3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="E8" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="3">
-        <v>50</v>
-      </c>
-      <c r="H8" s="3">
-        <v>100</v>
-      </c>
-      <c r="I8" s="3">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3">
-        <v>30</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2</v>
-      </c>
-      <c r="L8" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="N8" s="3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="E9" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="3">
-        <v>250</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2</v>
-      </c>
-      <c r="J9" s="3">
-        <v>150</v>
-      </c>
-      <c r="K9" s="3">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="M9" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="P11" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="E10" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="3">
-        <v>200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3">
-        <v>280</v>
-      </c>
-      <c r="K10" s="3">
-        <v>4</v>
-      </c>
-      <c r="L10" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="N10" s="3">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="E11" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="3">
-        <v>300</v>
-      </c>
-      <c r="H11" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I11" s="3">
-        <v>1</v>
-      </c>
-      <c r="J11" s="3">
-        <v>450</v>
-      </c>
-      <c r="K11" s="3">
-        <v>5</v>
-      </c>
-      <c r="L11" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="M11" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="N11" s="3">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="15.75" customHeight="1">
+    <row r="12" spans="1:16" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
     </row>
-    <row r="13" spans="1:14" ht="15.75" customHeight="1">
+    <row r="13" spans="1:16" ht="15.75" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
     </row>
-    <row r="14" spans="1:14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:16" ht="15.75" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" customHeight="1">
+    <row r="15" spans="1:16" ht="15.75" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" customHeight="1">
+    <row r="16" spans="1:16" ht="15.75" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A54448A-2350-4677-A544-4A8B2BD45E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB63D6A9-99C2-4B08-A6A5-48361A19397B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="885" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3660" yWindow="660" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
   <si>
     <t>Name</t>
   </si>
@@ -400,6 +400,10 @@
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_Shell</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_PistolBullet</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1006,7 +1010,7 @@
     <col min="4" max="4" width="10.7109375" style="3" customWidth="1"/>
     <col min="5" max="5" width="44.42578125" style="3" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="51.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="61.5703125" style="3" customWidth="1"/>
     <col min="8" max="8" width="19.5703125" style="3" customWidth="1"/>
     <col min="9" max="11" width="12.5703125" style="3"/>
     <col min="12" max="12" width="15.85546875" style="3" customWidth="1"/>
@@ -1158,13 +1162,13 @@
         <v>20</v>
       </c>
       <c r="J4" s="3">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="K4" s="3">
         <v>2</v>
       </c>
       <c r="L4" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M4" s="3">
         <v>2</v>
@@ -1191,21 +1195,25 @@
         <v>23</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+        <v>54</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="4">
+        <v>7</v>
+      </c>
       <c r="I5" s="3">
         <v>15</v>
       </c>
       <c r="J5" s="3">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="K5" s="3">
         <v>4</v>
       </c>
       <c r="L5" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="M5" s="3">
         <v>5</v>
@@ -1240,13 +1248,13 @@
         <v>10</v>
       </c>
       <c r="J6" s="3">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="K6" s="3">
         <v>3</v>
       </c>
       <c r="L6" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M6" s="3">
         <v>1</v>
@@ -1285,7 +1293,7 @@
         <v>50</v>
       </c>
       <c r="J7" s="3">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="K7" s="3">
         <v>3</v>
@@ -1326,7 +1334,7 @@
         <v>50</v>
       </c>
       <c r="J8" s="3">
-        <v>100</v>
+        <v>750</v>
       </c>
       <c r="K8" s="3">
         <v>4</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB63D6A9-99C2-4B08-A6A5-48361A19397B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB8F195-D2B6-4A9C-BCC3-813BCDF5E0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="660" windowWidth="31110" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5745" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
   <si>
     <t>Name</t>
   </si>
@@ -151,30 +151,6 @@
   </si>
   <si>
     <r>
-      <t>Prefabs/Enemy/Enemy_Prefab/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Police</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_Prefab</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>f</t>
     </r>
     <r>
@@ -204,38 +180,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Prefabs/Enemy/Enemy_Prefab/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Athlete</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_Prefab</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>enemy_soldiergun_01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>군인(총)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Prefabs/Enemy/Enemy_Prefab/SoldierGun_Prefab</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -244,10 +192,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>군인(칼)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Prefabs/Enemy/Enemy_Prefab/SoldierKnife_Prefab</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -261,18 +205,6 @@
   </si>
   <si>
     <t>enemy_drill_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>탱크</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염탱크</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>드릴</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -363,18 +295,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>시민</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>경찰</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>운동선수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Instance</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -404,6 +324,234 @@
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_PistolBullet</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Agent_Prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Police_Prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Athlete_Prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_agent_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시민</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>경찰</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>운동선수</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>군인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>총</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>군인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>칼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>탱크</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화염탱크</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>드릴</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>특수요원</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PointAttack</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PointAttackDelay</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackRange</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Enemy_PointAttack_Grenade</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -411,7 +559,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -456,6 +604,21 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -557,19 +720,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -580,13 +737,25 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1001,7 +1170,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:P996"/>
+  <dimension ref="A1:R996"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
@@ -1014,14 +1183,14 @@
     <col min="8" max="8" width="19.5703125" style="3" customWidth="1"/>
     <col min="9" max="11" width="12.5703125" style="3"/>
     <col min="12" max="12" width="15.85546875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="17" style="3" customWidth="1"/>
-    <col min="14" max="14" width="18.140625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="12.5703125" style="3"/>
+    <col min="13" max="15" width="17" style="3" customWidth="1"/>
+    <col min="16" max="16" width="18.140625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="17.5703125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" customHeight="1">
+    <row r="1" spans="1:18" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1035,13 +1204,13 @@
       <c r="E1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:16" ht="12.75">
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="2" spans="1:18" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1057,530 +1226,612 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="12" t="s">
         <v>21</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="8" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="O2" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="P2" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="N3" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="15">
+        <v>20</v>
+      </c>
+      <c r="J4" s="15">
+        <v>70</v>
+      </c>
+      <c r="K4" s="15">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="L4" s="15">
+        <v>5</v>
+      </c>
+      <c r="M4" s="15">
+        <v>2</v>
+      </c>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="Q4" s="15">
         <v>1</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="R4" s="15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A5" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="17">
         <v>7</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" s="11" t="s">
+      <c r="I5" s="15">
         <v>15</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="J5" s="15">
+        <v>150</v>
+      </c>
+      <c r="K5" s="15">
+        <v>4</v>
+      </c>
+      <c r="L5" s="15">
+        <v>30</v>
+      </c>
+      <c r="M5" s="15">
+        <v>5</v>
+      </c>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="Q5" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="R5" s="15">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A6" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="15">
+        <v>10</v>
+      </c>
+      <c r="J6" s="15">
+        <v>100</v>
+      </c>
+      <c r="K6" s="15">
+        <v>3</v>
+      </c>
+      <c r="L6" s="15">
+        <v>15</v>
+      </c>
+      <c r="M6" s="15">
+        <v>1</v>
+      </c>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="Q6" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="R6" s="15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="B7" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="G7" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="H7" s="17">
+        <v>7</v>
+      </c>
+      <c r="I7" s="15">
+        <v>50</v>
+      </c>
+      <c r="J7" s="15">
+        <v>500</v>
+      </c>
+      <c r="K7" s="15">
+        <v>3</v>
+      </c>
+      <c r="L7" s="15">
+        <v>15</v>
+      </c>
+      <c r="M7" s="15">
+        <v>4</v>
+      </c>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="Q7" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="R7" s="15">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A8" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="15">
+        <v>50</v>
+      </c>
+      <c r="J8" s="15">
+        <v>750</v>
+      </c>
+      <c r="K8" s="15">
+        <v>4</v>
+      </c>
+      <c r="L8" s="15">
+        <v>30</v>
+      </c>
+      <c r="M8" s="15">
+        <v>2</v>
+      </c>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="R8" s="15">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A9" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="3">
-        <v>20</v>
-      </c>
-      <c r="J4" s="3">
-        <v>70</v>
-      </c>
-      <c r="K4" s="3">
+      <c r="H9" s="17">
+        <v>5</v>
+      </c>
+      <c r="I9" s="15">
+        <v>250</v>
+      </c>
+      <c r="J9" s="15">
+        <v>1500</v>
+      </c>
+      <c r="K9" s="15">
         <v>2</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L9" s="15">
+        <v>150</v>
+      </c>
+      <c r="M9" s="15">
+        <v>3</v>
+      </c>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="Q9" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="R9" s="15">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A10" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="15">
+        <v>200</v>
+      </c>
+      <c r="J10" s="15">
+        <v>1000</v>
+      </c>
+      <c r="K10" s="15">
+        <v>3</v>
+      </c>
+      <c r="L10" s="15">
+        <v>280</v>
+      </c>
+      <c r="M10" s="15">
+        <v>4</v>
+      </c>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="Q10" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="R10" s="15">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A11" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="15">
+        <v>300</v>
+      </c>
+      <c r="J11" s="15">
+        <v>3000</v>
+      </c>
+      <c r="K11" s="15">
+        <v>1</v>
+      </c>
+      <c r="L11" s="15">
+        <v>450</v>
+      </c>
+      <c r="M11" s="15">
         <v>5</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="Q11" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="R11" s="15">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A12" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="15">
+        <v>3</v>
+      </c>
+      <c r="I12" s="15">
+        <v>500</v>
+      </c>
+      <c r="J12" s="15">
+        <v>5500</v>
+      </c>
+      <c r="K12" s="15">
         <v>2</v>
       </c>
-      <c r="N4" s="3">
+      <c r="L12" s="15">
+        <v>800</v>
+      </c>
+      <c r="M12" s="15">
+        <v>7</v>
+      </c>
+      <c r="N12" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="O12" s="15">
+        <v>3</v>
+      </c>
+      <c r="P12" s="15">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="O4" s="3">
-        <v>1</v>
-      </c>
-      <c r="P4" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="E5" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="4">
-        <v>7</v>
-      </c>
-      <c r="I5" s="3">
-        <v>15</v>
-      </c>
-      <c r="J5" s="3">
-        <v>150</v>
-      </c>
-      <c r="K5" s="3">
-        <v>4</v>
-      </c>
-      <c r="L5" s="3">
-        <v>30</v>
-      </c>
-      <c r="M5" s="3">
-        <v>5</v>
-      </c>
-      <c r="N5" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="O5" s="3">
+      <c r="Q12" s="15">
         <v>0.05</v>
       </c>
-      <c r="P5" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="E6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="3">
-        <v>10</v>
-      </c>
-      <c r="J6" s="3">
-        <v>100</v>
-      </c>
-      <c r="K6" s="3">
-        <v>3</v>
-      </c>
-      <c r="L6" s="3">
-        <v>15</v>
-      </c>
-      <c r="M6" s="3">
-        <v>1</v>
-      </c>
-      <c r="N6" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="O6" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="P6" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="E7" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" s="4">
-        <v>7</v>
-      </c>
-      <c r="I7" s="3">
-        <v>50</v>
-      </c>
-      <c r="J7" s="3">
-        <v>500</v>
-      </c>
-      <c r="K7" s="3">
-        <v>3</v>
-      </c>
-      <c r="L7" s="3">
-        <v>15</v>
-      </c>
-      <c r="M7" s="3">
-        <v>4</v>
-      </c>
-      <c r="N7" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="O7" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="P7" s="3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="E8" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="3">
-        <v>50</v>
-      </c>
-      <c r="J8" s="3">
-        <v>750</v>
-      </c>
-      <c r="K8" s="3">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3">
-        <v>30</v>
-      </c>
-      <c r="M8" s="3">
-        <v>2</v>
-      </c>
-      <c r="N8" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="P8" s="3">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="E9" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="4">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3">
-        <v>250</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K9" s="3">
-        <v>2</v>
-      </c>
-      <c r="L9" s="3">
-        <v>150</v>
-      </c>
-      <c r="M9" s="3">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="O9" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="P9" s="3">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="E10" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="3">
-        <v>200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K10" s="3">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3">
-        <v>280</v>
-      </c>
-      <c r="M10" s="3">
-        <v>4</v>
-      </c>
-      <c r="N10" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="O10" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="P10" s="3">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="E11" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="3">
-        <v>300</v>
-      </c>
-      <c r="J11" s="3">
-        <v>3000</v>
-      </c>
-      <c r="K11" s="3">
-        <v>1</v>
-      </c>
-      <c r="L11" s="3">
-        <v>450</v>
-      </c>
-      <c r="M11" s="3">
-        <v>5</v>
-      </c>
-      <c r="N11" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="O11" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="P11" s="3">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-    </row>
-    <row r="13" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-    </row>
-    <row r="14" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-    </row>
-    <row r="15" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-    </row>
-    <row r="16" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+      <c r="R12" s="15">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:18" ht="15.75" customHeight="1">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB8F195-D2B6-4A9C-BCC3-813BCDF5E0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DA81DF-56E7-41D4-9314-B0892ABE3CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5745" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="330" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -324,10 +324,6 @@
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_PistolBullet</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Enemy/Enemy_Prefab/Agent_Prefab</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -517,41 +513,157 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
+    <t>PointAttack</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PointAttackDelay</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackRange</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Enemy_PointAttack_Grenade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PointAttackType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Throw</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수요원(수류탄)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_agent_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
         <family val="3"/>
         <charset val="129"/>
-        <scheme val="minor"/>
       </rPr>
       <t>특수요원</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>PointAttack</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>PointAttackDelay</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>AttackRange</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Enemy/Enemy_Prefab/Enemy_PointAttack_Grenade</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>레이저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_agent_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/GrenadeAgent_Prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/LaserAgent_Prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>지점공격인경우만</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_Laser</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>특수요원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방패</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/ShieldAgent_Prefab</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>투사체 있는 경우만</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -559,7 +671,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -619,6 +731,13 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="8">
@@ -720,7 +839,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -756,6 +875,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1170,7 +1292,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:R996"/>
+  <dimension ref="A1:S996"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
@@ -1178,19 +1300,19 @@
     <col min="3" max="3" width="16.42578125" style="3" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" style="3" customWidth="1"/>
     <col min="5" max="5" width="44.42578125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="61.5703125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" style="3" customWidth="1"/>
-    <col min="9" max="11" width="12.5703125" style="3"/>
-    <col min="12" max="12" width="15.85546875" style="3" customWidth="1"/>
-    <col min="13" max="15" width="17" style="3" customWidth="1"/>
-    <col min="16" max="16" width="18.140625" style="3" customWidth="1"/>
-    <col min="17" max="17" width="17.5703125" style="3" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" style="3" customWidth="1"/>
-    <col min="19" max="16384" width="12.5703125" style="3"/>
+    <col min="6" max="7" width="19.5703125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="61.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="19.5703125" style="3" customWidth="1"/>
+    <col min="10" max="12" width="12.5703125" style="3"/>
+    <col min="13" max="13" width="15.85546875" style="3" customWidth="1"/>
+    <col min="14" max="16" width="17" style="3" customWidth="1"/>
+    <col min="17" max="17" width="18.140625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="17.5703125" style="3" customWidth="1"/>
+    <col min="19" max="19" width="17.140625" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" customHeight="1">
+    <row r="1" spans="1:19" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1208,9 +1330,20 @@
         <v>17</v>
       </c>
       <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="H1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="2" spans="1:18" ht="12.75">
+    <row r="2" spans="1:19" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1229,13 +1362,13 @@
       <c r="F2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J2" s="11" t="s">
@@ -1248,25 +1381,28 @@
         <v>22</v>
       </c>
       <c r="M2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="11" t="s">
-        <v>62</v>
-      </c>
       <c r="O2" s="11" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="Q2" s="11" t="s">
         <v>35</v>
       </c>
       <c r="R2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="3" spans="1:19" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
@@ -1285,49 +1421,52 @@
       <c r="F3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="J3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="N3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="9" t="s">
-        <v>63</v>
-      </c>
       <c r="O3" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P3" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="R3" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="S3" s="9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1">
+    <row r="4" spans="1:19" ht="15.75" customHeight="1">
       <c r="A4" s="14" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="15"/>
@@ -1338,132 +1477,135 @@
         <v>40</v>
       </c>
       <c r="G4" s="14"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="15">
+      <c r="H4" s="14"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="15">
         <v>20</v>
       </c>
-      <c r="J4" s="15">
+      <c r="K4" s="15">
         <v>70</v>
       </c>
-      <c r="K4" s="15">
+      <c r="L4" s="15">
         <v>2</v>
       </c>
-      <c r="L4" s="15">
+      <c r="M4" s="15">
         <v>5</v>
       </c>
-      <c r="M4" s="15">
+      <c r="N4" s="15">
         <v>2</v>
       </c>
-      <c r="N4" s="15"/>
       <c r="O4" s="15"/>
-      <c r="P4" s="15">
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="Q4" s="15">
+      <c r="R4" s="15">
         <v>1</v>
       </c>
-      <c r="R4" s="15">
+      <c r="S4" s="15">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1">
+    <row r="5" spans="1:19" ht="15.75" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="14"/>
+      <c r="H5" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="17">
+      <c r="I5" s="17">
         <v>7</v>
       </c>
-      <c r="I5" s="15">
+      <c r="J5" s="15">
         <v>15</v>
       </c>
-      <c r="J5" s="15">
+      <c r="K5" s="15">
         <v>150</v>
       </c>
-      <c r="K5" s="15">
+      <c r="L5" s="15">
         <v>4</v>
       </c>
-      <c r="L5" s="15">
+      <c r="M5" s="15">
         <v>30</v>
       </c>
-      <c r="M5" s="15">
+      <c r="N5" s="15">
         <v>5</v>
       </c>
-      <c r="N5" s="15"/>
       <c r="O5" s="15"/>
-      <c r="P5" s="15">
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="Q5" s="15">
+      <c r="R5" s="15">
         <v>0.05</v>
       </c>
-      <c r="R5" s="15">
+      <c r="S5" s="15">
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15.75" customHeight="1">
+    <row r="6" spans="1:19" ht="15.75" customHeight="1">
       <c r="A6" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G6" s="14"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="15">
+      <c r="H6" s="14"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="15">
         <v>10</v>
       </c>
-      <c r="J6" s="15">
+      <c r="K6" s="15">
         <v>100</v>
       </c>
-      <c r="K6" s="15">
+      <c r="L6" s="15">
         <v>3</v>
       </c>
-      <c r="L6" s="15">
+      <c r="M6" s="15">
         <v>15</v>
       </c>
-      <c r="M6" s="15">
+      <c r="N6" s="15">
         <v>1</v>
       </c>
-      <c r="N6" s="15"/>
       <c r="O6" s="15"/>
-      <c r="P6" s="15">
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="Q6" s="15">
+      <c r="R6" s="15">
         <v>0.05</v>
       </c>
-      <c r="R6" s="15">
+      <c r="S6" s="15">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="15.75" customHeight="1">
+    <row r="7" spans="1:19" ht="15.75" customHeight="1">
       <c r="A7" s="18" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="15"/>
@@ -1473,45 +1615,46 @@
       <c r="F7" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="14"/>
+      <c r="H7" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="17">
+      <c r="I7" s="17">
         <v>7</v>
       </c>
-      <c r="I7" s="15">
+      <c r="J7" s="15">
         <v>50</v>
       </c>
-      <c r="J7" s="15">
+      <c r="K7" s="15">
         <v>500</v>
       </c>
-      <c r="K7" s="15">
+      <c r="L7" s="15">
         <v>3</v>
       </c>
-      <c r="L7" s="15">
+      <c r="M7" s="15">
         <v>15</v>
       </c>
-      <c r="M7" s="15">
+      <c r="N7" s="15">
         <v>4</v>
       </c>
-      <c r="N7" s="15"/>
       <c r="O7" s="15"/>
-      <c r="P7" s="15">
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="Q7" s="15">
+      <c r="R7" s="15">
         <v>0.05</v>
       </c>
-      <c r="R7" s="15">
+      <c r="S7" s="15">
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15.75" customHeight="1">
+    <row r="8" spans="1:19" ht="15.75" customHeight="1">
       <c r="A8" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="15"/>
@@ -1522,40 +1665,41 @@
         <v>40</v>
       </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="15">
+      <c r="H8" s="14"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="15">
         <v>50</v>
       </c>
-      <c r="J8" s="15">
+      <c r="K8" s="15">
         <v>750</v>
       </c>
-      <c r="K8" s="15">
+      <c r="L8" s="15">
         <v>4</v>
       </c>
-      <c r="L8" s="15">
+      <c r="M8" s="15">
         <v>30</v>
       </c>
-      <c r="M8" s="15">
+      <c r="N8" s="15">
         <v>2</v>
       </c>
-      <c r="N8" s="15"/>
       <c r="O8" s="15"/>
-      <c r="P8" s="15">
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="Q8" s="15">
+      <c r="R8" s="15">
         <v>0.05</v>
       </c>
-      <c r="R8" s="15">
+      <c r="S8" s="15">
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="15.75" customHeight="1">
+    <row r="9" spans="1:19" ht="15.75" customHeight="1">
       <c r="A9" s="14" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="15"/>
@@ -1565,45 +1709,46 @@
       <c r="F9" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="14"/>
+      <c r="H9" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="17">
+      <c r="I9" s="17">
         <v>5</v>
       </c>
-      <c r="I9" s="15">
+      <c r="J9" s="15">
         <v>250</v>
       </c>
-      <c r="J9" s="15">
+      <c r="K9" s="15">
         <v>1500</v>
       </c>
-      <c r="K9" s="15">
+      <c r="L9" s="15">
         <v>2</v>
       </c>
-      <c r="L9" s="15">
+      <c r="M9" s="15">
         <v>150</v>
       </c>
-      <c r="M9" s="15">
+      <c r="N9" s="15">
         <v>3</v>
       </c>
-      <c r="N9" s="15"/>
       <c r="O9" s="15"/>
-      <c r="P9" s="15">
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="Q9" s="15">
+      <c r="R9" s="15">
         <v>0.05</v>
       </c>
-      <c r="R9" s="15">
+      <c r="S9" s="15">
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15.75" customHeight="1">
+    <row r="10" spans="1:19" ht="15.75" customHeight="1">
       <c r="A10" s="18" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="18"/>
       <c r="D10" s="15"/>
@@ -1614,40 +1759,41 @@
         <v>40</v>
       </c>
       <c r="G10" s="14"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="15">
+      <c r="H10" s="14"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="15">
         <v>200</v>
       </c>
-      <c r="J10" s="15">
+      <c r="K10" s="15">
         <v>1000</v>
       </c>
-      <c r="K10" s="15">
+      <c r="L10" s="15">
         <v>3</v>
       </c>
-      <c r="L10" s="15">
+      <c r="M10" s="15">
         <v>280</v>
       </c>
-      <c r="M10" s="15">
+      <c r="N10" s="15">
         <v>4</v>
       </c>
-      <c r="N10" s="15"/>
       <c r="O10" s="15"/>
-      <c r="P10" s="15">
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="Q10" s="15">
+      <c r="R10" s="15">
         <v>0.05</v>
       </c>
-      <c r="R10" s="15">
+      <c r="S10" s="15">
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15.75" customHeight="1">
+    <row r="11" spans="1:19" ht="15.75" customHeight="1">
       <c r="A11" s="18" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="15"/>
@@ -1658,102 +1804,181 @@
         <v>40</v>
       </c>
       <c r="G11" s="14"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="15">
+      <c r="H11" s="14"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="15">
         <v>300</v>
       </c>
-      <c r="J11" s="15">
+      <c r="K11" s="15">
         <v>3000</v>
       </c>
-      <c r="K11" s="15">
+      <c r="L11" s="15">
         <v>1</v>
       </c>
-      <c r="L11" s="15">
+      <c r="M11" s="15">
         <v>450</v>
       </c>
-      <c r="M11" s="15">
+      <c r="N11" s="15">
         <v>5</v>
       </c>
-      <c r="N11" s="15"/>
       <c r="O11" s="15"/>
-      <c r="P11" s="15">
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="Q11" s="15">
+      <c r="R11" s="15">
         <v>0.05</v>
       </c>
-      <c r="R11" s="15">
+      <c r="S11" s="15">
         <v>3000</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15.75" customHeight="1">
+    <row r="12" spans="1:19" ht="15.75" customHeight="1">
       <c r="A12" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" s="15">
+        <v>67</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="15">
         <v>3</v>
       </c>
-      <c r="I12" s="15">
+      <c r="J12" s="15">
         <v>500</v>
       </c>
-      <c r="J12" s="15">
+      <c r="K12" s="15">
         <v>5500</v>
       </c>
-      <c r="K12" s="15">
+      <c r="L12" s="15">
         <v>2</v>
       </c>
-      <c r="L12" s="15">
+      <c r="M12" s="15">
         <v>800</v>
       </c>
-      <c r="M12" s="15">
+      <c r="N12" s="15">
+        <v>10</v>
+      </c>
+      <c r="O12" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="P12" s="15">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="R12" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="S12" s="15">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A13" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="E13" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="3">
         <v>7</v>
       </c>
-      <c r="N12" s="15">
-        <v>2.5</v>
-      </c>
-      <c r="O12" s="15">
+      <c r="J13" s="3">
+        <v>500</v>
+      </c>
+      <c r="K13" s="3">
+        <v>5500</v>
+      </c>
+      <c r="L13" s="3">
         <v>3</v>
       </c>
-      <c r="P12" s="15">
+      <c r="M13" s="3">
+        <v>750</v>
+      </c>
+      <c r="N13" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="Q12" s="15">
+      <c r="R13" s="3">
         <v>0.05</v>
       </c>
-      <c r="R12" s="15">
+      <c r="S13" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+    <row r="14" spans="1:19" ht="15.75" customHeight="1">
+      <c r="A14" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="E14" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="J14" s="3">
+        <v>500</v>
+      </c>
+      <c r="K14" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L14" s="3">
+        <v>1</v>
+      </c>
+      <c r="M14" s="3">
+        <v>300</v>
+      </c>
+      <c r="N14" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="S14" s="3">
+        <v>6000</v>
+      </c>
     </row>
-    <row r="14" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:18" ht="15.75" customHeight="1">
+    <row r="15" spans="1:19" ht="15.75" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
-    <row r="16" spans="1:18" ht="15.75" customHeight="1">
+    <row r="16" spans="1:19" ht="15.75" customHeight="1">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DA81DF-56E7-41D4-9314-B0892ABE3CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F99A655-13B8-4E76-B920-F8E211E012DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="330" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="95">
   <si>
     <t>Name</t>
   </si>
@@ -47,19 +47,19 @@
   </si>
   <si>
     <t>적 설명</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>적 Icon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>적 프리팹</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EnemyType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -74,7 +74,7 @@
       </rPr>
       <t>xpReward</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -89,7 +89,7 @@
       </rPr>
       <t>p</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -104,7 +104,7 @@
       </rPr>
       <t>oveSpeed</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -119,35 +119,35 @@
       </rPr>
       <t>ttackDamage</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enemy_citizen_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>적 정보</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enemy_police_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enemy_athlete_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Citizen_Prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>float</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -162,7 +162,7 @@
       </rPr>
       <t>loat</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -177,47 +177,47 @@
       </rPr>
       <t>ttackCoolDown</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enemy_soldiergun_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/SoldierGun_Prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enemy_soldierknife_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/SoldierKnife_Prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enemy_tank_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enemy_firetank_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enemy_drill_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Tank_Prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/FireTank_Prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Drill_Prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -232,7 +232,7 @@
       </rPr>
       <t xml:space="preserve">loat </t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -247,7 +247,7 @@
       </rPr>
       <t>nt</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -262,7 +262,7 @@
       </rPr>
       <t>ropHealKitChance</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -277,7 +277,7 @@
       </rPr>
       <t>ropUmbraChance</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -292,51 +292,51 @@
       </rPr>
       <t>ropUmbraAmount</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Instance</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ProjectilePath</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ProjectileSpeed</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Projectile</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_Bullet</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_Shell</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_PistolBullet</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Police_Prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Athlete_Prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enemy_agent_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -350,7 +350,7 @@
       </rPr>
       <t>시민</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -364,7 +364,7 @@
       </rPr>
       <t>경찰</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -378,7 +378,7 @@
       </rPr>
       <t>운동선수</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -423,7 +423,7 @@
       </rPr>
       <t>)</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -468,7 +468,7 @@
       </rPr>
       <t>)</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -482,7 +482,7 @@
       </rPr>
       <t>탱크</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -496,7 +496,7 @@
       </rPr>
       <t>화염탱크</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -510,51 +510,51 @@
       </rPr>
       <t>드릴</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>PointAttack</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>float</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>PointAttackDelay</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>AttackRange</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>float</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Enemy_PointAttack_Grenade</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>PointAttackType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Throw</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>특수요원(수류탄)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enemy_agent_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -595,27 +595,27 @@
       </rPr>
       <t>)</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>enemy_agent_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/GrenadeAgent_Prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/LaserAgent_Prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>지점공격인경우만</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_Laser</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -656,26 +656,330 @@
       </rPr>
       <t>)</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/ShieldAgent_Prefab</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>투사체 있는 경우만</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nemy_subject_01</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실험체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>01</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Subject01_Prefab</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nemy_subject_02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nemy_subject_03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nemy_subject_04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nemy_subject_05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실험체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실험체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실험체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실험체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Subject02_Prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Subject03_Prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Subject04_Prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Subject05_Prefab</t>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nstance</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -841,43 +1145,43 @@
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1974,91 +2278,144 @@
       </c>
     </row>
     <row r="15" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+      <c r="A15" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>80</v>
+      </c>
       <c r="C15" s="4"/>
+      <c r="E15" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="16" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
+      <c r="A16" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>86</v>
+      </c>
       <c r="C16" s="4"/>
+      <c r="E16" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A17" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>87</v>
+      </c>
       <c r="C17" s="4"/>
+      <c r="E17" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A18" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>88</v>
+      </c>
       <c r="C18" s="4"/>
+      <c r="E18" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A19" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>89</v>
+      </c>
       <c r="C19" s="4"/>
+      <c r="E19" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>94</v>
+      </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1">
+    <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1">
+    <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
     </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
     </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
     </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1">
+    <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
     </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
     </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1">
+    <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
     </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1">
+    <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
     </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1">
+    <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
     </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1">
+    <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
     </row>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1">
+    <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
     </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -3024,7 +3381,7 @@
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F99A655-13B8-4E76-B920-F8E211E012DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E9B406-F91E-46BE-9E7B-045B2A4AE5FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="96">
   <si>
     <t>Name</t>
   </si>
@@ -960,6 +960,10 @@
       </rPr>
       <t>nstance</t>
     </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_EnergyBlade</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2291,6 +2295,30 @@
       <c r="F15" s="11" t="s">
         <v>40</v>
       </c>
+      <c r="J15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K15" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L15" s="3">
+        <v>5</v>
+      </c>
+      <c r="M15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N15" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="S15" s="3">
+        <v>15000</v>
+      </c>
     </row>
     <row r="16" spans="1:19" ht="15.75" customHeight="1">
       <c r="A16" s="22" t="s">
@@ -2306,8 +2334,38 @@
       <c r="F16" s="11" t="s">
         <v>44</v>
       </c>
+      <c r="H16" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="I16" s="3">
+        <v>10</v>
+      </c>
+      <c r="J16" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K16" s="3">
+        <v>12000</v>
+      </c>
+      <c r="L16" s="3">
+        <v>3</v>
+      </c>
+      <c r="M16" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N16" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="R16" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="S16" s="3">
+        <v>15000</v>
+      </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+    <row r="17" spans="1:19" ht="15.75" customHeight="1">
       <c r="A17" s="22" t="s">
         <v>83</v>
       </c>
@@ -2321,8 +2379,32 @@
       <c r="F17" s="11" t="s">
         <v>40</v>
       </c>
+      <c r="J17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K17" s="3">
+        <v>30000</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1</v>
+      </c>
+      <c r="M17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N17" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="S17" s="3">
+        <v>15000</v>
+      </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+    <row r="18" spans="1:19" ht="15.75" customHeight="1">
       <c r="A18" s="22" t="s">
         <v>84</v>
       </c>
@@ -2336,8 +2418,32 @@
       <c r="F18" s="11" t="s">
         <v>40</v>
       </c>
+      <c r="J18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>9000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>7</v>
+      </c>
+      <c r="M18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N18" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="S18" s="3">
+        <v>15000</v>
+      </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1">
+    <row r="19" spans="1:19" ht="15.75" customHeight="1">
       <c r="A19" s="22" t="s">
         <v>85</v>
       </c>
@@ -2354,68 +2460,98 @@
       <c r="G19" s="11" t="s">
         <v>94</v>
       </c>
+      <c r="J19" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K19" s="3">
+        <v>23000</v>
+      </c>
+      <c r="L19" s="3">
+        <v>4</v>
+      </c>
+      <c r="M19" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N19" s="3">
+        <v>9</v>
+      </c>
+      <c r="O19" s="3">
+        <v>3</v>
+      </c>
+      <c r="P19" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="R19" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="S19" s="3">
+        <v>15000</v>
+      </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1">
+    <row r="20" spans="1:19" ht="15.75" customHeight="1">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+    <row r="21" spans="1:19" ht="15.75" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+    <row r="22" spans="1:19" ht="15.75" customHeight="1">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
     </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+    <row r="23" spans="1:19" ht="15.75" customHeight="1">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+    <row r="24" spans="1:19" ht="15.75" customHeight="1">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+    <row r="25" spans="1:19" ht="15.75" customHeight="1">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1">
+    <row r="26" spans="1:19" ht="15.75" customHeight="1">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
     </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1">
+    <row r="27" spans="1:19" ht="15.75" customHeight="1">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
     </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1">
+    <row r="28" spans="1:19" ht="15.75" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
     </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1">
+    <row r="29" spans="1:19" ht="15.75" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1">
+    <row r="30" spans="1:19" ht="15.75" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1">
+    <row r="31" spans="1:19" ht="15.75" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:19" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E9B406-F91E-46BE-9E7B-045B2A4AE5FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5B1A3E-6C50-4E66-8903-09F2E4BAF723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="97">
   <si>
     <t>Name</t>
   </si>
@@ -964,6 +964,10 @@
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_EnergyBlade</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Enemy_PointAttack_Tentacle</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1788,7 +1792,7 @@
       <c r="H4" s="14"/>
       <c r="I4" s="17"/>
       <c r="J4" s="15">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K4" s="15">
         <v>70</v>
@@ -1837,7 +1841,7 @@
         <v>7</v>
       </c>
       <c r="J5" s="15">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K5" s="15">
         <v>150</v>
@@ -1882,7 +1886,7 @@
       <c r="H6" s="14"/>
       <c r="I6" s="17"/>
       <c r="J6" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K6" s="15">
         <v>100</v>
@@ -1931,7 +1935,7 @@
         <v>7</v>
       </c>
       <c r="J7" s="15">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K7" s="15">
         <v>500</v>
@@ -1976,7 +1980,7 @@
       <c r="H8" s="14"/>
       <c r="I8" s="17"/>
       <c r="J8" s="15">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K8" s="15">
         <v>750</v>
@@ -2025,7 +2029,7 @@
         <v>5</v>
       </c>
       <c r="J9" s="15">
-        <v>250</v>
+        <v>23</v>
       </c>
       <c r="K9" s="15">
         <v>1500</v>
@@ -2070,7 +2074,7 @@
       <c r="H10" s="14"/>
       <c r="I10" s="17"/>
       <c r="J10" s="15">
-        <v>200</v>
+        <v>23</v>
       </c>
       <c r="K10" s="15">
         <v>1000</v>
@@ -2115,7 +2119,7 @@
       <c r="H11" s="14"/>
       <c r="I11" s="17"/>
       <c r="J11" s="15">
-        <v>300</v>
+        <v>23</v>
       </c>
       <c r="K11" s="15">
         <v>3000</v>
@@ -2166,7 +2170,7 @@
         <v>3</v>
       </c>
       <c r="J12" s="15">
-        <v>500</v>
+        <v>57</v>
       </c>
       <c r="K12" s="15">
         <v>5500</v>
@@ -2217,7 +2221,7 @@
         <v>7</v>
       </c>
       <c r="J13" s="3">
-        <v>500</v>
+        <v>57</v>
       </c>
       <c r="K13" s="3">
         <v>5500</v>
@@ -2257,7 +2261,7 @@
       </c>
       <c r="H14" s="15"/>
       <c r="J14" s="3">
-        <v>500</v>
+        <v>57</v>
       </c>
       <c r="K14" s="3">
         <v>10000</v>
@@ -2296,7 +2300,7 @@
         <v>40</v>
       </c>
       <c r="J15" s="3">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>15000</v>
@@ -2341,7 +2345,7 @@
         <v>10</v>
       </c>
       <c r="J16" s="3">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="K16" s="3">
         <v>12000</v>
@@ -2380,7 +2384,7 @@
         <v>40</v>
       </c>
       <c r="J17" s="3">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="K17" s="3">
         <v>30000</v>
@@ -2419,7 +2423,7 @@
         <v>40</v>
       </c>
       <c r="J18" s="3">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="K18" s="3">
         <v>9000</v>
@@ -2460,8 +2464,11 @@
       <c r="G19" s="11" t="s">
         <v>94</v>
       </c>
+      <c r="H19" s="15" t="s">
+        <v>96</v>
+      </c>
       <c r="J19" s="3">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="K19" s="3">
         <v>23000</v>
@@ -2473,13 +2480,13 @@
         <v>2500</v>
       </c>
       <c r="N19" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O19" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P19" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="3">
         <v>2.5000000000000001E-2</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5B1A3E-6C50-4E66-8903-09F2E4BAF723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6C9099-E9B5-49A6-978D-ACC689D4C442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-150" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="103">
   <si>
     <t>Name</t>
   </si>
@@ -541,10 +541,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>PointAttackType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Throw</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -968,6 +964,74 @@
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Enemy_PointAttack_Tentacle</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nemy_type_01</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변이체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>01</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Type01_Prefab</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ombing</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>대쉬인경우 대쉬 속도</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>자폭인경우 자폭 속도</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1617,7 +1681,9 @@
     <col min="9" max="9" width="19.5703125" style="3" customWidth="1"/>
     <col min="10" max="12" width="12.5703125" style="3"/>
     <col min="13" max="13" width="15.85546875" style="3" customWidth="1"/>
-    <col min="14" max="16" width="17" style="3" customWidth="1"/>
+    <col min="14" max="14" width="17" style="3" customWidth="1"/>
+    <col min="15" max="15" width="19.85546875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="17" style="3" customWidth="1"/>
     <col min="17" max="17" width="18.140625" style="3" customWidth="1"/>
     <col min="18" max="18" width="17.5703125" style="3" customWidth="1"/>
     <col min="19" max="19" width="17.140625" style="3" customWidth="1"/>
@@ -1643,16 +1709,16 @@
       </c>
       <c r="G1" s="10"/>
       <c r="H1" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="P1" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="12.75">
@@ -1734,7 +1800,7 @@
         <v>11</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>42</v>
@@ -2150,18 +2216,18 @@
         <v>50</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>59</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>64</v>
@@ -2202,20 +2268,20 @@
     </row>
     <row r="13" spans="1:19" ht="15.75" customHeight="1">
       <c r="A13" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>69</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>70</v>
       </c>
       <c r="C13" s="4"/>
       <c r="E13" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>44</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I13" s="3">
         <v>7</v>
@@ -2247,14 +2313,14 @@
     </row>
     <row r="14" spans="1:19" ht="15.75" customHeight="1">
       <c r="A14" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C14" s="4"/>
       <c r="E14" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>40</v>
@@ -2287,14 +2353,14 @@
     </row>
     <row r="15" spans="1:19" ht="15.75" customHeight="1">
       <c r="A15" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="23" t="s">
         <v>79</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>80</v>
       </c>
       <c r="C15" s="4"/>
       <c r="E15" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>40</v>
@@ -2326,20 +2392,20 @@
     </row>
     <row r="16" spans="1:19" ht="15.75" customHeight="1">
       <c r="A16" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" s="4"/>
       <c r="E16" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>44</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I16" s="3">
         <v>10</v>
@@ -2371,14 +2437,14 @@
     </row>
     <row r="17" spans="1:19" ht="15.75" customHeight="1">
       <c r="A17" s="22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C17" s="4"/>
       <c r="E17" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>40</v>
@@ -2410,14 +2476,14 @@
     </row>
     <row r="18" spans="1:19" ht="15.75" customHeight="1">
       <c r="A18" s="22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18" s="4"/>
       <c r="E18" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>40</v>
@@ -2449,23 +2515,23 @@
     </row>
     <row r="19" spans="1:19" ht="15.75" customHeight="1">
       <c r="A19" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C19" s="4"/>
       <c r="E19" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>59</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J19" s="3">
         <v>100</v>
@@ -2499,9 +2565,22 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
+      <c r="A20" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>97</v>
+      </c>
       <c r="C20" s="4"/>
+      <c r="E20" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="21" spans="1:19" ht="15.75" customHeight="1">
       <c r="A21" s="4"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6C9099-E9B5-49A6-978D-ACC689D4C442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7173D58E-FEFF-43C1-96D6-CE951B01C592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-150" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1005" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="113">
   <si>
     <t>Name</t>
   </si>
@@ -1032,6 +1032,201 @@
   </si>
   <si>
     <t>자폭인경우 자폭 속도</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nemy_type_02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nemy_type_03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nemy_type_04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변이체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변이체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변이체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Type02_Prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Type03_Prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Type04_Prefab</t>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ash</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2581,21 +2776,162 @@
       <c r="G20" s="11" t="s">
         <v>100</v>
       </c>
+      <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="S20" s="3">
+        <v>20000</v>
+      </c>
     </row>
     <row r="21" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
+      <c r="A21" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>106</v>
+      </c>
       <c r="C21" s="4"/>
+      <c r="E21" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J21" s="3">
+        <v>200</v>
+      </c>
+      <c r="K21" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L21" s="3">
+        <v>2</v>
+      </c>
+      <c r="M21" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N21" s="3">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="S21" s="3">
+        <v>20000</v>
+      </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
+      <c r="A22" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>107</v>
+      </c>
       <c r="C22" s="5"/>
+      <c r="E22" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="I22" s="3">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
+        <v>200</v>
+      </c>
+      <c r="K22" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L22" s="3">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N22" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="S22" s="3">
+        <v>20000</v>
+      </c>
     </row>
     <row r="23" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
+      <c r="A23" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>108</v>
+      </c>
       <c r="C23" s="5"/>
+      <c r="E23" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J23" s="3">
+        <v>200</v>
+      </c>
+      <c r="K23" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L23" s="3">
+        <v>1</v>
+      </c>
+      <c r="M23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N23" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="S23" s="3">
+        <v>20000</v>
+      </c>
     </row>
     <row r="24" spans="1:19" ht="15.75" customHeight="1">
       <c r="A24" s="5"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7173D58E-FEFF-43C1-96D6-CE951B01C592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1559DDDB-BB52-40E3-B608-12C5A8D266EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4275" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="114">
   <si>
     <t>Name</t>
   </si>
@@ -1227,6 +1227,10 @@
       </rPr>
       <t>ash</t>
     </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Enemy/Enemy_Prefab/Enemy_PointAttack_Paranoia</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2446,10 +2450,10 @@
         <v>10</v>
       </c>
       <c r="O12" s="15">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="P12" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="15">
         <v>2.5000000000000001E-2</v>
@@ -2744,7 +2748,7 @@
         <v>4</v>
       </c>
       <c r="O19" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P19" s="3">
         <v>1</v>
@@ -2792,7 +2796,7 @@
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="3">
         <v>2.5000000000000001E-2</v>
@@ -2821,6 +2825,9 @@
       <c r="G21" s="11" t="s">
         <v>40</v>
       </c>
+      <c r="H21" s="15" t="s">
+        <v>113</v>
+      </c>
       <c r="J21" s="3">
         <v>200</v>
       </c>
@@ -2836,8 +2843,11 @@
       <c r="N21" s="3">
         <v>5</v>
       </c>
+      <c r="O21" s="3">
+        <v>1</v>
+      </c>
       <c r="P21" s="3">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" s="3">
         <v>2.5000000000000001E-2</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1559DDDB-BB52-40E3-B608-12C5A8D266EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82182BC0-A303-473D-8ADF-F4D900709E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4275" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2751,7 +2751,7 @@
         <v>1</v>
       </c>
       <c r="P19" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="3">
         <v>2.5000000000000001E-2</v>
@@ -2877,7 +2877,7 @@
         <v>112</v>
       </c>
       <c r="I22" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" s="3">
         <v>200</v>
@@ -2893,6 +2893,9 @@
       </c>
       <c r="N22" s="3">
         <v>4</v>
+      </c>
+      <c r="P22" s="3">
+        <v>1.2</v>
       </c>
       <c r="Q22" s="3">
         <v>2.5000000000000001E-2</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82182BC0-A303-473D-8ADF-F4D900709E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05EF7EB-C8CA-4EF1-8A1E-D64458311B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4275" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2793,7 +2793,7 @@
         <v>10000</v>
       </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="O20" s="3">
         <v>1</v>
@@ -2877,7 +2877,7 @@
         <v>112</v>
       </c>
       <c r="I22" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J22" s="3">
         <v>200</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05EF7EB-C8CA-4EF1-8A1E-D64458311B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25C07EB-FAF9-413B-842C-55A5BF521B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4275" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="116">
   <si>
     <t>Name</t>
   </si>
@@ -1231,6 +1231,25 @@
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Enemy_PointAttack_Paranoia</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ropMagnetChance</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1867,7 +1886,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:S996"/>
+  <dimension ref="A1:T996"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
@@ -1886,10 +1905,11 @@
     <col min="17" max="17" width="18.140625" style="3" customWidth="1"/>
     <col min="18" max="18" width="17.5703125" style="3" customWidth="1"/>
     <col min="19" max="19" width="17.140625" style="3" customWidth="1"/>
-    <col min="20" max="16384" width="12.5703125" style="3"/>
+    <col min="20" max="20" width="18.28515625" style="3" customWidth="1"/>
+    <col min="21" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" customHeight="1">
+    <row r="1" spans="1:20" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1920,7 +1940,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="12.75">
+    <row r="2" spans="1:20" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1978,8 +1998,11 @@
       <c r="S2" s="11" t="s">
         <v>36</v>
       </c>
+      <c r="T2" s="11" t="s">
+        <v>115</v>
+      </c>
     </row>
-    <row r="3" spans="1:19" s="8" customFormat="1" ht="15.75" customHeight="1">
+    <row r="3" spans="1:20" s="8" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
@@ -2037,8 +2060,11 @@
       <c r="S3" s="9" t="s">
         <v>39</v>
       </c>
+      <c r="T3" s="9" t="s">
+        <v>114</v>
+      </c>
     </row>
-    <row r="4" spans="1:19" ht="15.75" customHeight="1">
+    <row r="4" spans="1:20" ht="15.75" customHeight="1">
       <c r="A4" s="14" t="s">
         <v>16</v>
       </c>
@@ -2074,7 +2100,7 @@
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
       <c r="Q4" s="15">
-        <v>2.5000000000000001E-2</v>
+        <v>1</v>
       </c>
       <c r="R4" s="15">
         <v>1</v>
@@ -2082,8 +2108,11 @@
       <c r="S4" s="15">
         <v>100</v>
       </c>
+      <c r="T4" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1">
+    <row r="5" spans="1:20" ht="15.75" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>18</v>
       </c>
@@ -2131,8 +2160,11 @@
       <c r="S5" s="15">
         <v>150</v>
       </c>
+      <c r="T5" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="6" spans="1:19" ht="15.75" customHeight="1">
+    <row r="6" spans="1:20" ht="15.75" customHeight="1">
       <c r="A6" s="18" t="s">
         <v>19</v>
       </c>
@@ -2176,8 +2208,11 @@
       <c r="S6" s="15">
         <v>100</v>
       </c>
+      <c r="T6" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="7" spans="1:19" ht="15.75" customHeight="1">
+    <row r="7" spans="1:20" ht="15.75" customHeight="1">
       <c r="A7" s="18" t="s">
         <v>25</v>
       </c>
@@ -2225,8 +2260,11 @@
       <c r="S7" s="15">
         <v>500</v>
       </c>
+      <c r="T7" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="8" spans="1:19" ht="15.75" customHeight="1">
+    <row r="8" spans="1:20" ht="15.75" customHeight="1">
       <c r="A8" s="18" t="s">
         <v>27</v>
       </c>
@@ -2270,8 +2308,11 @@
       <c r="S8" s="15">
         <v>500</v>
       </c>
+      <c r="T8" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="9" spans="1:19" ht="15.75" customHeight="1">
+    <row r="9" spans="1:20" ht="15.75" customHeight="1">
       <c r="A9" s="14" t="s">
         <v>29</v>
       </c>
@@ -2319,8 +2360,11 @@
       <c r="S9" s="15">
         <v>3000</v>
       </c>
+      <c r="T9" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="10" spans="1:19" ht="15.75" customHeight="1">
+    <row r="10" spans="1:20" ht="15.75" customHeight="1">
       <c r="A10" s="18" t="s">
         <v>30</v>
       </c>
@@ -2364,8 +2408,11 @@
       <c r="S10" s="15">
         <v>3000</v>
       </c>
+      <c r="T10" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="11" spans="1:19" ht="15.75" customHeight="1">
+    <row r="11" spans="1:20" ht="15.75" customHeight="1">
       <c r="A11" s="18" t="s">
         <v>31</v>
       </c>
@@ -2409,8 +2456,11 @@
       <c r="S11" s="15">
         <v>3000</v>
       </c>
+      <c r="T11" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="12" spans="1:19" ht="15.75" customHeight="1">
+    <row r="12" spans="1:20" ht="15.75" customHeight="1">
       <c r="A12" s="20" t="s">
         <v>50</v>
       </c>
@@ -2464,8 +2514,11 @@
       <c r="S12" s="15">
         <v>5000</v>
       </c>
+      <c r="T12" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="13" spans="1:19" ht="15.75" customHeight="1">
+    <row r="13" spans="1:20" ht="15.75" customHeight="1">
       <c r="A13" s="22" t="s">
         <v>68</v>
       </c>
@@ -2509,8 +2562,11 @@
       <c r="S13" s="3">
         <v>5000</v>
       </c>
+      <c r="T13" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="14" spans="1:19" ht="15.75" customHeight="1">
+    <row r="14" spans="1:20" ht="15.75" customHeight="1">
       <c r="A14" s="22" t="s">
         <v>70</v>
       </c>
@@ -2549,8 +2605,11 @@
       <c r="S14" s="3">
         <v>6000</v>
       </c>
+      <c r="T14" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="15" spans="1:19" ht="15.75" customHeight="1">
+    <row r="15" spans="1:20" ht="15.75" customHeight="1">
       <c r="A15" s="22" t="s">
         <v>78</v>
       </c>
@@ -2588,8 +2647,11 @@
       <c r="S15" s="3">
         <v>15000</v>
       </c>
+      <c r="T15" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="16" spans="1:19" ht="15.75" customHeight="1">
+    <row r="16" spans="1:20" ht="15.75" customHeight="1">
       <c r="A16" s="22" t="s">
         <v>81</v>
       </c>
@@ -2633,8 +2695,11 @@
       <c r="S16" s="3">
         <v>15000</v>
       </c>
+      <c r="T16" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="17" spans="1:19" ht="15.75" customHeight="1">
+    <row r="17" spans="1:20" ht="15.75" customHeight="1">
       <c r="A17" s="22" t="s">
         <v>82</v>
       </c>
@@ -2672,8 +2737,11 @@
       <c r="S17" s="3">
         <v>15000</v>
       </c>
+      <c r="T17" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="18" spans="1:19" ht="15.75" customHeight="1">
+    <row r="18" spans="1:20" ht="15.75" customHeight="1">
       <c r="A18" s="22" t="s">
         <v>83</v>
       </c>
@@ -2711,8 +2779,11 @@
       <c r="S18" s="3">
         <v>15000</v>
       </c>
+      <c r="T18" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="19" spans="1:19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:20" ht="15.75" customHeight="1">
       <c r="A19" s="22" t="s">
         <v>84</v>
       </c>
@@ -2762,8 +2833,11 @@
       <c r="S19" s="3">
         <v>15000</v>
       </c>
+      <c r="T19" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="20" spans="1:19" ht="15.75" customHeight="1">
+    <row r="20" spans="1:20" ht="15.75" customHeight="1">
       <c r="A20" s="22" t="s">
         <v>96</v>
       </c>
@@ -2807,8 +2881,11 @@
       <c r="S20" s="3">
         <v>20000</v>
       </c>
+      <c r="T20" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="21" spans="1:19" ht="15.75" customHeight="1">
+    <row r="21" spans="1:20" ht="15.75" customHeight="1">
       <c r="A21" s="22" t="s">
         <v>103</v>
       </c>
@@ -2858,8 +2935,11 @@
       <c r="S21" s="3">
         <v>20000</v>
       </c>
+      <c r="T21" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="22" spans="1:19" ht="15.75" customHeight="1">
+    <row r="22" spans="1:20" ht="15.75" customHeight="1">
       <c r="A22" s="22" t="s">
         <v>104</v>
       </c>
@@ -2906,8 +2986,11 @@
       <c r="S22" s="3">
         <v>20000</v>
       </c>
+      <c r="T22" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="23" spans="1:19" ht="15.75" customHeight="1">
+    <row r="23" spans="1:20" ht="15.75" customHeight="1">
       <c r="A23" s="22" t="s">
         <v>105</v>
       </c>
@@ -2945,48 +3028,51 @@
       <c r="S23" s="3">
         <v>20000</v>
       </c>
+      <c r="T23" s="15">
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
-    <row r="24" spans="1:19" ht="15.75" customHeight="1">
+    <row r="24" spans="1:20" ht="15.75" customHeight="1">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
     </row>
-    <row r="25" spans="1:19" ht="15.75" customHeight="1">
+    <row r="25" spans="1:20" ht="15.75" customHeight="1">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
     </row>
-    <row r="26" spans="1:19" ht="15.75" customHeight="1">
+    <row r="26" spans="1:20" ht="15.75" customHeight="1">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
     </row>
-    <row r="27" spans="1:19" ht="15.75" customHeight="1">
+    <row r="27" spans="1:20" ht="15.75" customHeight="1">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
     </row>
-    <row r="28" spans="1:19" ht="15.75" customHeight="1">
+    <row r="28" spans="1:20" ht="15.75" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
     </row>
-    <row r="29" spans="1:19" ht="15.75" customHeight="1">
+    <row r="29" spans="1:20" ht="15.75" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
     </row>
-    <row r="30" spans="1:19" ht="15.75" customHeight="1">
+    <row r="30" spans="1:20" ht="15.75" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
     </row>
-    <row r="31" spans="1:19" ht="15.75" customHeight="1">
+    <row r="31" spans="1:20" ht="15.75" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
     </row>
-    <row r="32" spans="1:19" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:20" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25C07EB-FAF9-413B-842C-55A5BF521B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF6F7C5-6622-4A08-B7D9-8F43E95287A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4275" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17550" yWindow="1380" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="137">
   <si>
     <t>Name</t>
   </si>
@@ -1250,6 +1250,1889 @@
   </si>
   <si>
     <t>float</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>비록 전투능력은 떨어지지만 지구를 지키기 위해 나서는 시민이다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>지구를 지키기 위해 가장 먼저 출동한 경찰이다. 권총을 사용한다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 시민에 비해 신체능력이 뛰어나며 주먹을 사용한다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>군대가 투입되며 출동한 군인이다. 돌격소총을 사용하여 공격한다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>군대가 투입되면 출동한 군인이다. 검술을 사용하여 공격한다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>내구성이 뛰어나며 전방의 드릴은 엄청난 파괴력을 갖고 있다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전방의 화염방사기로 공격하여 상대를 녹여버린다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>포를 발사하여 공격한다. 사거리가 길고 엄청난 위력을 갖고 있다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수임무를 맡고 있는 요원이다. 수류탄을 던지며 그 위력은 엄청나다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수임무를 맡고 있는 요원이다. 레이저를 발사하며 공격속도가 빠르다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수임무를 맡고 있는 요원이다. 큰 방패로 적을 밀쳐내며 엄청난 내구성을 갖고 있다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인간개발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로젝트의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실험체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>날카로운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>손톱으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>베어버린다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준수한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>능력을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자랑한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간개발 프로젝트의 실험체02이다. 외계의 힘을 사용가능하며 날카로운 칼날을 소환하여 공격한다. 피격 시 끔찍한 고통이 따라온다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인간개발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로젝트의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실험체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거대한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>망치를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내려쳐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격하며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위력은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상당하다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>느리지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>엄청난</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내구성을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>갖고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인간개발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로젝트의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실험체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빠른</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속도로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>교란하며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거대한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>칼날을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꺼내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">인간개발 프로젝트의 실험에05이다. 외계의 힘을 사용하여 바닥에서 촉수를 소환해 공격한다. </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변이가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일어난</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변이체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빠르게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돌진해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자폭하여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발 도중 변이가 일어난 변이체02이다. 적의 위치에 암흑지대를 소환하고 암흑지대의 피해를 받으면 끔찍한 고통을 느낀다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변이가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일어난</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변이체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빠르게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돌진하여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공격하며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속도는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인간이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감당할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변이가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일어난</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변이체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거대한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>몸에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>손이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>튀어나와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강하게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내리친다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파괴력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>앞에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>버틸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>존재는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogue_Image/EnemyUnit_Icon/</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1433,14 +3316,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1465,13 +3347,15 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1891,8 +3775,8 @@
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="120.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="45.42578125" style="3" customWidth="1"/>
     <col min="5" max="5" width="44.42578125" style="3" customWidth="1"/>
     <col min="6" max="7" width="19.5703125" style="3" customWidth="1"/>
     <col min="8" max="8" width="61.5703125" style="3" customWidth="1"/>
@@ -1923,20 +3807,20 @@
       <c r="E1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10" t="s">
+      <c r="G1" s="9"/>
+      <c r="H1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="9" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1956,10 +3840,10 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>65</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -1968,571 +3852,612 @@
       <c r="I2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="Q2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="R2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="S2" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="T2" s="10" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="8" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:20" s="7" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="P3" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="Q3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="S3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="T3" s="8" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15" t="s">
+      <c r="C4" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="15">
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="14">
         <v>5</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="14">
         <v>70</v>
       </c>
-      <c r="L4" s="15">
+      <c r="L4" s="14">
         <v>2</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4" s="14">
         <v>5</v>
       </c>
-      <c r="N4" s="15">
+      <c r="N4" s="14">
         <v>2</v>
       </c>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15">
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14">
         <v>1</v>
       </c>
-      <c r="R4" s="15">
+      <c r="R4" s="14">
         <v>1</v>
       </c>
-      <c r="S4" s="15">
+      <c r="S4" s="14">
         <v>100</v>
       </c>
-      <c r="T4" s="15">
+      <c r="T4" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
+      <c r="C5" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14" t="s">
+      <c r="G5" s="13"/>
+      <c r="H5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="16">
         <v>7</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="14">
         <v>5</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="14">
         <v>150</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="14">
         <v>4</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="14">
         <v>30</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="14">
         <v>5</v>
       </c>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15">
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="R5" s="15">
+      <c r="R5" s="14">
         <v>0.05</v>
       </c>
-      <c r="S5" s="15">
+      <c r="S5" s="14">
         <v>150</v>
       </c>
-      <c r="T5" s="15">
+      <c r="T5" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15" t="s">
+      <c r="C6" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="15">
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="14">
         <v>5</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="14">
         <v>100</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="14">
         <v>3</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="14">
         <v>15</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="14">
         <v>1</v>
       </c>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15">
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="R6" s="15">
+      <c r="R6" s="14">
         <v>0.05</v>
       </c>
-      <c r="S6" s="15">
+      <c r="S6" s="14">
         <v>100</v>
       </c>
-      <c r="T6" s="15">
+      <c r="T6" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15" t="s">
+      <c r="C7" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14" t="s">
+      <c r="G7" s="13"/>
+      <c r="H7" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="16">
         <v>7</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="14">
         <v>10</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="14">
         <v>500</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="14">
         <v>3</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="14">
         <v>15</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="14">
         <v>4</v>
       </c>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15">
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="R7" s="15">
+      <c r="R7" s="14">
         <v>0.05</v>
       </c>
-      <c r="S7" s="15">
+      <c r="S7" s="14">
         <v>500</v>
       </c>
-      <c r="T7" s="15">
+      <c r="T7" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15" t="s">
+      <c r="C8" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="15">
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="14">
         <v>10</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="14">
         <v>750</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="14">
         <v>4</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="14">
         <v>30</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="14">
         <v>2</v>
       </c>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15">
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="R8" s="15">
+      <c r="R8" s="14">
         <v>0.05</v>
       </c>
-      <c r="S8" s="15">
+      <c r="S8" s="14">
         <v>500</v>
       </c>
-      <c r="T8" s="15">
+      <c r="T8" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15" t="s">
+      <c r="C9" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14" t="s">
+      <c r="G9" s="13"/>
+      <c r="H9" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="16">
         <v>5</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="14">
         <v>23</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="14">
         <v>1500</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="14">
         <v>2</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="14">
         <v>150</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="14">
         <v>3</v>
       </c>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15">
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="R9" s="15">
+      <c r="R9" s="14">
         <v>0.05</v>
       </c>
-      <c r="S9" s="15">
+      <c r="S9" s="14">
         <v>3000</v>
       </c>
-      <c r="T9" s="15">
+      <c r="T9" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15" t="s">
+      <c r="C10" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="15">
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="14">
         <v>23</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="14">
         <v>1000</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="14">
         <v>3</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="14">
         <v>280</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="14">
         <v>4</v>
       </c>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15">
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="R10" s="15">
+      <c r="R10" s="14">
         <v>0.05</v>
       </c>
-      <c r="S10" s="15">
+      <c r="S10" s="14">
         <v>3000</v>
       </c>
-      <c r="T10" s="15">
+      <c r="T10" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15" t="s">
+      <c r="C11" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="15">
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="14">
         <v>23</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="14">
         <v>3000</v>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="14">
         <v>1</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="14">
         <v>450</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="14">
         <v>5</v>
       </c>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15">
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="R11" s="15">
+      <c r="R11" s="14">
         <v>0.05</v>
       </c>
-      <c r="S11" s="15">
+      <c r="S11" s="14">
         <v>3000</v>
       </c>
-      <c r="T11" s="15">
+      <c r="T11" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15" t="s">
+      <c r="C12" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="14">
         <v>3</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="14">
         <v>57</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="14">
         <v>5500</v>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="14">
         <v>2</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12" s="14">
         <v>800</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="14">
         <v>10</v>
       </c>
-      <c r="O12" s="15">
+      <c r="O12" s="14">
         <v>10</v>
       </c>
-      <c r="P12" s="15">
+      <c r="P12" s="14">
         <v>2</v>
       </c>
-      <c r="Q12" s="15">
+      <c r="Q12" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="R12" s="15">
+      <c r="R12" s="14">
         <v>0.05</v>
       </c>
-      <c r="S12" s="15">
+      <c r="S12" s="14">
         <v>5000</v>
       </c>
-      <c r="T12" s="15">
+      <c r="T12" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="E13" s="15" t="s">
+      <c r="C13" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="14" t="s">
         <v>74</v>
       </c>
       <c r="I13" s="3">
@@ -2562,25 +4487,30 @@
       <c r="S13" s="3">
         <v>5000</v>
       </c>
-      <c r="T13" s="15">
+      <c r="T13" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="E14" s="15" t="s">
+      <c r="C14" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="15"/>
+      <c r="H14" s="14"/>
       <c r="J14" s="3">
         <v>57</v>
       </c>
@@ -2605,22 +4535,27 @@
       <c r="S14" s="3">
         <v>6000</v>
       </c>
-      <c r="T14" s="15">
+      <c r="T14" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="E15" s="11" t="s">
+      <c r="C15" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="10" t="s">
         <v>40</v>
       </c>
       <c r="J15" s="3">
@@ -2647,25 +4582,30 @@
       <c r="S15" s="3">
         <v>15000</v>
       </c>
-      <c r="T15" s="15">
+      <c r="T15" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="E16" s="11" t="s">
+      <c r="C16" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="14" t="s">
         <v>94</v>
       </c>
       <c r="I16" s="3">
@@ -2695,22 +4635,27 @@
       <c r="S16" s="3">
         <v>15000</v>
       </c>
-      <c r="T16" s="15">
+      <c r="T16" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="E17" s="11" t="s">
+      <c r="C17" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>40</v>
       </c>
       <c r="J17" s="3">
@@ -2737,22 +4682,27 @@
       <c r="S17" s="3">
         <v>15000</v>
       </c>
-      <c r="T17" s="15">
+      <c r="T17" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="E18" s="11" t="s">
+      <c r="C18" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="10" t="s">
         <v>40</v>
       </c>
       <c r="J18" s="3">
@@ -2779,28 +4729,33 @@
       <c r="S18" s="3">
         <v>15000</v>
       </c>
-      <c r="T18" s="15">
+      <c r="T18" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="E19" s="11" t="s">
+      <c r="C19" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="14" t="s">
         <v>95</v>
       </c>
       <c r="J19" s="3">
@@ -2833,25 +4788,30 @@
       <c r="S19" s="3">
         <v>15000</v>
       </c>
-      <c r="T19" s="15">
+      <c r="T19" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="E20" s="11" t="s">
+      <c r="C20" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="10" t="s">
         <v>100</v>
       </c>
       <c r="J20" s="3">
@@ -2881,28 +4841,33 @@
       <c r="S20" s="3">
         <v>20000</v>
       </c>
-      <c r="T20" s="15">
+      <c r="T20" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="E21" s="11" t="s">
+      <c r="C21" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="H21" s="14" t="s">
         <v>113</v>
       </c>
       <c r="J21" s="3">
@@ -2935,25 +4900,30 @@
       <c r="S21" s="3">
         <v>20000</v>
       </c>
-      <c r="T21" s="15">
+      <c r="T21" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="E22" s="11" t="s">
+      <c r="C22" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="10" t="s">
         <v>112</v>
       </c>
       <c r="I22" s="3">
@@ -2986,22 +4956,27 @@
       <c r="S22" s="3">
         <v>20000</v>
       </c>
-      <c r="T22" s="15">
+      <c r="T22" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="E23" s="11" t="s">
+      <c r="C23" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="10" t="s">
         <v>40</v>
       </c>
       <c r="J23" s="3">
@@ -3028,49 +5003,49 @@
       <c r="S23" s="3">
         <v>20000</v>
       </c>
-      <c r="T23" s="15">
+      <c r="T23" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
     </row>
     <row r="25" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
     </row>
     <row r="26" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
     </row>
     <row r="27" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
     </row>
     <row r="28" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
     </row>
     <row r="29" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
     </row>
     <row r="30" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
     </row>
     <row r="31" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
     </row>
     <row r="32" spans="1:20" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF6F7C5-6622-4A08-B7D9-8F43E95287A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4849C832-76DC-4723-B5D6-4F6CC269E01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17550" yWindow="1380" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3540" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="156">
   <si>
     <t>Name</t>
   </si>
@@ -545,55 +545,10 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>특수요원(수류탄)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>enemy_agent_02</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>특수요원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>레이저</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>enemy_agent_03</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -611,47 +566,6 @@
   </si>
   <si>
     <t>Prefabs/Enemy/Enemy_Prefab/Enemy_Projectile_Laser</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>특수요원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>방패</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -3132,7 +3046,95 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Dialogue_Image/EnemyUnit_Icon/</t>
+    <t>Icon/EnemyUnit_Icon/Citizen</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Police</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Athlete</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/SoldierGun</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/SoldierKnife</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Tank</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Drill</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/FireTank</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/GrenadeAgent</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/LaserAgent</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Subject01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/ShieldAgent</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Subject02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Subject03</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Subject04</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Subject05</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Type01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Type03</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Type04</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Type02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>수류탄요원</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>레이저요원</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>방패요원</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3316,7 +3318,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3356,6 +3358,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3777,7 +3780,7 @@
     <col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
     <col min="3" max="3" width="120.5703125" style="3" customWidth="1"/>
     <col min="4" max="4" width="45.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="44.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="48.5703125" style="3" customWidth="1"/>
     <col min="6" max="7" width="19.5703125" style="3" customWidth="1"/>
     <col min="8" max="8" width="61.5703125" style="3" customWidth="1"/>
     <col min="9" max="9" width="19.5703125" style="3" customWidth="1"/>
@@ -3812,16 +3815,16 @@
       </c>
       <c r="G1" s="9"/>
       <c r="H1" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="12.75">
@@ -3883,7 +3886,7 @@
         <v>36</v>
       </c>
       <c r="T2" s="10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:20" s="7" customFormat="1" ht="15.75" customHeight="1">
@@ -3906,7 +3909,7 @@
         <v>11</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>42</v>
@@ -3945,7 +3948,7 @@
         <v>39</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15.75" customHeight="1">
@@ -3956,10 +3959,10 @@
         <v>51</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>20</v>
@@ -4008,10 +4011,10 @@
         <v>52</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>48</v>
@@ -4064,10 +4067,10 @@
         <v>53</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>49</v>
@@ -4116,7 +4119,7 @@
         <v>54</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>136</v>
@@ -4172,10 +4175,10 @@
         <v>55</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>28</v>
@@ -4224,10 +4227,10 @@
         <v>56</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>32</v>
@@ -4280,10 +4283,10 @@
         <v>57</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>33</v>
@@ -4332,10 +4335,10 @@
         <v>58</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>34</v>
@@ -4381,16 +4384,16 @@
         <v>50</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>59</v>
@@ -4440,25 +4443,25 @@
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1">
       <c r="A13" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>154</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I13" s="3">
         <v>7</v>
@@ -4493,19 +4496,19 @@
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>75</v>
+        <v>68</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>155</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>40</v>
@@ -4541,19 +4544,19 @@
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>40</v>
@@ -4588,25 +4591,25 @@
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1">
       <c r="A16" s="20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>44</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I16" s="3">
         <v>10</v>
@@ -4641,19 +4644,19 @@
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>40</v>
@@ -4688,19 +4691,19 @@
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1">
       <c r="A18" s="20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>40</v>
@@ -4735,28 +4738,28 @@
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1">
       <c r="A19" s="20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>59</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J19" s="3">
         <v>100</v>
@@ -4794,25 +4797,25 @@
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1">
       <c r="A20" s="20" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>40</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="J20" s="3">
         <v>200</v>
@@ -4847,19 +4850,19 @@
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1">
       <c r="A21" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="C21" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>106</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>109</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>59</v>
@@ -4868,7 +4871,7 @@
         <v>40</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="J21" s="3">
         <v>200</v>
@@ -4906,25 +4909,25 @@
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1">
       <c r="A22" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="C22" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>107</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>40</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I22" s="3">
         <v>10</v>
@@ -4962,19 +4965,19 @@
     </row>
     <row r="23" spans="1:20" ht="15.75" customHeight="1">
       <c r="A23" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="C23" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>108</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>111</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>40</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4849C832-76DC-4723-B5D6-4F6CC269E01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB60E68-3EC8-41A7-9315-147A951D30CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3540" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="570" yWindow="75" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="162">
   <si>
     <t>Name</t>
   </si>
@@ -3135,6 +3135,499 @@
   </si>
   <si>
     <t>방패요원</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nemy_boss_eclipse</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이클립스</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종말</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로젝트의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결과물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Project.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이클립스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지금까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주인공의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전투</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>온전한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>형태의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로젝트가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>완성된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결과물이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이클립스를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이길</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>존재는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>것</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnemyUnit_Icon/Eclipse</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>refabs/Enenmy/Enemy_Prefab/Eclipse_Prefab</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>oss</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3318,7 +3811,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3359,6 +3852,9 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3778,7 +4274,7 @@
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="120.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="151.28515625" style="3" customWidth="1"/>
     <col min="4" max="4" width="45.42578125" style="3" customWidth="1"/>
     <col min="5" max="5" width="48.5703125" style="3" customWidth="1"/>
     <col min="6" max="7" width="19.5703125" style="3" customWidth="1"/>
@@ -5011,9 +5507,63 @@
       </c>
     </row>
     <row r="24" spans="1:20" ht="15.75" customHeight="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
+      <c r="A24" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" s="3">
+        <v>10</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>500000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3">
+        <v>1</v>
+      </c>
+      <c r="P24" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:20" ht="15.75" customHeight="1">
       <c r="A25" s="4"/>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB60E68-3EC8-41A7-9315-147A951D30CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602AEE00-4C30-432C-9841-7FED6CC8EDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="75" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6690" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="162">
   <si>
     <t>Name</t>
   </si>
@@ -3602,6 +3602,21 @@
   </si>
   <si>
     <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>oss</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>P</t>
     </r>
     <r>
@@ -3611,22 +3626,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>refabs/Enenmy/Enemy_Prefab/Eclipse_Prefab</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>oss</t>
+      <t>refabs/Enemy/Enemy_Prefab/Eclipse_Prefab</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -5520,14 +5520,12 @@
         <v>159</v>
       </c>
       <c r="E24" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F24" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="F24" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>91</v>
-      </c>
+      <c r="H24" s="14"/>
       <c r="I24" s="3">
         <v>10</v>
       </c>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602AEE00-4C30-432C-9841-7FED6CC8EDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B429456C-190F-49B8-BB59-05433AC10EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6690" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="162">
   <si>
     <t>Name</t>
   </si>
@@ -5524,6 +5524,9 @@
       </c>
       <c r="F24" s="10" t="s">
         <v>160</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="3">

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B429456C-190F-49B8-BB59-05433AC10EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82E7F95-B6D1-431E-A0E5-9BCF1E1E4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6690" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4455" yWindow="375" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -4470,7 +4470,7 @@
       <c r="H4" s="13"/>
       <c r="I4" s="16"/>
       <c r="J4" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" s="14">
         <v>70</v>
@@ -4479,7 +4479,7 @@
         <v>2</v>
       </c>
       <c r="M4" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N4" s="14">
         <v>2</v>
@@ -4487,16 +4487,16 @@
       <c r="O4" s="14"/>
       <c r="P4" s="14"/>
       <c r="Q4" s="14">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="R4" s="14">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="S4" s="14">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="T4" s="14">
-        <v>1</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1">
@@ -4526,7 +4526,7 @@
         <v>7</v>
       </c>
       <c r="J5" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5" s="14">
         <v>150</v>
@@ -4535,7 +4535,7 @@
         <v>4</v>
       </c>
       <c r="M5" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N5" s="14">
         <v>5</v>
@@ -4543,16 +4543,16 @@
       <c r="O5" s="14"/>
       <c r="P5" s="14"/>
       <c r="Q5" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="R5" s="14">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="S5" s="14">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="T5" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1">
@@ -4578,16 +4578,16 @@
       <c r="H6" s="13"/>
       <c r="I6" s="16"/>
       <c r="J6" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K6" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="L6" s="14">
         <v>3</v>
       </c>
       <c r="M6" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N6" s="14">
         <v>1</v>
@@ -4595,16 +4595,16 @@
       <c r="O6" s="14"/>
       <c r="P6" s="14"/>
       <c r="Q6" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="R6" s="14">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="S6" s="14">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="T6" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1">
@@ -4634,16 +4634,16 @@
         <v>7</v>
       </c>
       <c r="J7" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K7" s="14">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L7" s="14">
         <v>3</v>
       </c>
       <c r="M7" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N7" s="14">
         <v>4</v>
@@ -4651,16 +4651,16 @@
       <c r="O7" s="14"/>
       <c r="P7" s="14"/>
       <c r="Q7" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="R7" s="14">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="S7" s="14">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="T7" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1">
@@ -4686,16 +4686,16 @@
       <c r="H8" s="13"/>
       <c r="I8" s="16"/>
       <c r="J8" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K8" s="14">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="L8" s="14">
         <v>4</v>
       </c>
       <c r="M8" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N8" s="14">
         <v>2</v>
@@ -4703,16 +4703,16 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="R8" s="14">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="S8" s="14">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="T8" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1">
@@ -4742,16 +4742,16 @@
         <v>5</v>
       </c>
       <c r="J9" s="14">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K9" s="14">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="L9" s="14">
         <v>2</v>
       </c>
       <c r="M9" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="N9" s="14">
         <v>3</v>
@@ -4759,16 +4759,16 @@
       <c r="O9" s="14"/>
       <c r="P9" s="14"/>
       <c r="Q9" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="R9" s="14">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="S9" s="14">
-        <v>3000</v>
+        <v>270</v>
       </c>
       <c r="T9" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1">
@@ -4794,16 +4794,16 @@
       <c r="H10" s="13"/>
       <c r="I10" s="16"/>
       <c r="J10" s="14">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K10" s="14">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L10" s="14">
         <v>3</v>
       </c>
       <c r="M10" s="14">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="N10" s="14">
         <v>4</v>
@@ -4811,16 +4811,16 @@
       <c r="O10" s="14"/>
       <c r="P10" s="14"/>
       <c r="Q10" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="R10" s="14">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="S10" s="14">
-        <v>3000</v>
+        <v>270</v>
       </c>
       <c r="T10" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" customHeight="1">
@@ -4846,16 +4846,16 @@
       <c r="H11" s="13"/>
       <c r="I11" s="16"/>
       <c r="J11" s="14">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K11" s="14">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="L11" s="14">
         <v>1</v>
       </c>
       <c r="M11" s="14">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="N11" s="14">
         <v>5</v>
@@ -4863,16 +4863,16 @@
       <c r="O11" s="14"/>
       <c r="P11" s="14"/>
       <c r="Q11" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="R11" s="14">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="S11" s="14">
-        <v>3000</v>
+        <v>270</v>
       </c>
       <c r="T11" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1">
@@ -4904,37 +4904,37 @@
         <v>3</v>
       </c>
       <c r="J12" s="14">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="K12" s="14">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="L12" s="14">
         <v>2</v>
       </c>
       <c r="M12" s="14">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="N12" s="14">
         <v>10</v>
       </c>
       <c r="O12" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P12" s="14">
         <v>2</v>
       </c>
       <c r="Q12" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="R12" s="14">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="S12" s="14">
-        <v>5000</v>
+        <v>600</v>
       </c>
       <c r="T12" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1">
@@ -4963,31 +4963,31 @@
         <v>7</v>
       </c>
       <c r="J13" s="3">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="K13" s="3">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="L13" s="3">
         <v>3</v>
       </c>
       <c r="M13" s="3">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="N13" s="3">
         <v>3</v>
       </c>
-      <c r="Q13" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="R13" s="3">
-        <v>0.05</v>
+      <c r="Q13" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="R13" s="14">
+        <v>0.35</v>
       </c>
       <c r="S13" s="3">
-        <v>5000</v>
+        <v>600</v>
       </c>
       <c r="T13" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1">
@@ -5011,31 +5011,31 @@
       </c>
       <c r="H14" s="14"/>
       <c r="J14" s="3">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="K14" s="3">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="L14" s="3">
         <v>1</v>
       </c>
       <c r="M14" s="3">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="N14" s="3">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0.05</v>
+      <c r="Q14" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="R14" s="14">
+        <v>0.35</v>
       </c>
       <c r="S14" s="3">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="T14" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1">
@@ -5058,31 +5058,31 @@
         <v>40</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K15" s="3">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="L15" s="3">
         <v>5</v>
       </c>
       <c r="M15" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N15" s="3">
         <v>4</v>
       </c>
-      <c r="Q15" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0.05</v>
+      <c r="Q15" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="R15" s="14">
+        <v>0.4</v>
       </c>
       <c r="S15" s="3">
-        <v>15000</v>
+        <v>1150</v>
       </c>
       <c r="T15" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1">
@@ -5111,31 +5111,31 @@
         <v>10</v>
       </c>
       <c r="J16" s="3">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K16" s="3">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="L16" s="3">
         <v>3</v>
       </c>
       <c r="M16" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="N16" s="3">
         <v>5</v>
       </c>
-      <c r="Q16" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="R16" s="3">
-        <v>0.05</v>
+      <c r="Q16" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="R16" s="14">
+        <v>0.4</v>
       </c>
       <c r="S16" s="3">
-        <v>15000</v>
+        <v>1150</v>
       </c>
       <c r="T16" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.75" customHeight="1">
@@ -5158,31 +5158,31 @@
         <v>40</v>
       </c>
       <c r="J17" s="3">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K17" s="3">
-        <v>30000</v>
+        <v>22000</v>
       </c>
       <c r="L17" s="3">
         <v>1</v>
       </c>
       <c r="M17" s="3">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="N17" s="3">
         <v>10</v>
       </c>
-      <c r="Q17" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="R17" s="3">
-        <v>0.05</v>
+      <c r="Q17" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="R17" s="14">
+        <v>0.4</v>
       </c>
       <c r="S17" s="3">
-        <v>15000</v>
+        <v>1150</v>
       </c>
       <c r="T17" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.75" customHeight="1">
@@ -5205,31 +5205,31 @@
         <v>40</v>
       </c>
       <c r="J18" s="3">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K18" s="3">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="L18" s="3">
         <v>7</v>
       </c>
       <c r="M18" s="3">
-        <v>1200</v>
+        <v>950</v>
       </c>
       <c r="N18" s="3">
         <v>2</v>
       </c>
-      <c r="Q18" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="R18" s="3">
-        <v>0.05</v>
+      <c r="Q18" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="R18" s="14">
+        <v>0.4</v>
       </c>
       <c r="S18" s="3">
-        <v>15000</v>
+        <v>1150</v>
       </c>
       <c r="T18" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.75" customHeight="1">
@@ -5258,16 +5258,16 @@
         <v>92</v>
       </c>
       <c r="J19" s="3">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K19" s="3">
-        <v>23000</v>
+        <v>17000</v>
       </c>
       <c r="L19" s="3">
         <v>4</v>
       </c>
       <c r="M19" s="3">
-        <v>2500</v>
+        <v>1900</v>
       </c>
       <c r="N19" s="3">
         <v>4</v>
@@ -5278,17 +5278,17 @@
       <c r="P19" s="3">
         <v>3</v>
       </c>
-      <c r="Q19" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="R19" s="3">
-        <v>0.05</v>
+      <c r="Q19" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="R19" s="14">
+        <v>0.4</v>
       </c>
       <c r="S19" s="3">
-        <v>15000</v>
+        <v>1150</v>
       </c>
       <c r="T19" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.75" customHeight="1">
@@ -5314,16 +5314,16 @@
         <v>97</v>
       </c>
       <c r="J20" s="3">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="K20" s="3">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="L20" s="3">
         <v>3</v>
       </c>
       <c r="M20" s="3">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="N20" s="3">
         <v>1</v>
@@ -5331,17 +5331,17 @@
       <c r="O20" s="3">
         <v>1</v>
       </c>
-      <c r="Q20" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0.05</v>
+      <c r="Q20" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="R20" s="14">
+        <v>0.45</v>
       </c>
       <c r="S20" s="3">
-        <v>20000</v>
+        <v>2200</v>
       </c>
       <c r="T20" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.75" customHeight="1">
@@ -5370,16 +5370,16 @@
         <v>110</v>
       </c>
       <c r="J21" s="3">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="K21" s="3">
-        <v>15000</v>
+        <v>11000</v>
       </c>
       <c r="L21" s="3">
         <v>2</v>
       </c>
       <c r="M21" s="3">
-        <v>3700</v>
+        <v>2800</v>
       </c>
       <c r="N21" s="3">
         <v>5</v>
@@ -5390,17 +5390,17 @@
       <c r="P21" s="3">
         <v>2.5</v>
       </c>
-      <c r="Q21" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="R21" s="3">
-        <v>0.05</v>
+      <c r="Q21" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="R21" s="14">
+        <v>0.45</v>
       </c>
       <c r="S21" s="3">
-        <v>20000</v>
+        <v>2200</v>
       </c>
       <c r="T21" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.75" customHeight="1">
@@ -5429,16 +5429,16 @@
         <v>10</v>
       </c>
       <c r="J22" s="3">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="K22" s="3">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="L22" s="3">
         <v>4</v>
       </c>
       <c r="M22" s="3">
-        <v>3500</v>
+        <v>2800</v>
       </c>
       <c r="N22" s="3">
         <v>4</v>
@@ -5446,17 +5446,17 @@
       <c r="P22" s="3">
         <v>1.2</v>
       </c>
-      <c r="Q22" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0.05</v>
+      <c r="Q22" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="R22" s="14">
+        <v>0.45</v>
       </c>
       <c r="S22" s="3">
-        <v>20000</v>
+        <v>2200</v>
       </c>
       <c r="T22" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="15.75" customHeight="1">
@@ -5479,31 +5479,31 @@
         <v>40</v>
       </c>
       <c r="J23" s="3">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="K23" s="3">
-        <v>50000</v>
+        <v>38000</v>
       </c>
       <c r="L23" s="3">
         <v>1</v>
       </c>
       <c r="M23" s="3">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="N23" s="3">
         <v>10</v>
       </c>
-      <c r="Q23" s="3">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="R23" s="3">
-        <v>0.05</v>
+      <c r="Q23" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="R23" s="14">
+        <v>0.45</v>
       </c>
       <c r="S23" s="3">
-        <v>20000</v>
+        <v>2200</v>
       </c>
       <c r="T23" s="14">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="15.75" customHeight="1">
@@ -5536,13 +5536,13 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>500000</v>
+        <v>3000000</v>
       </c>
       <c r="L24" s="3">
         <v>3</v>
       </c>
       <c r="M24" s="3">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="N24" s="3">
         <v>5</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82E7F95-B6D1-431E-A0E5-9BCF1E1E4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0D0F29-5D51-45DA-B0DB-1F083428078B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4455" yWindow="375" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5542,7 +5542,7 @@
         <v>3</v>
       </c>
       <c r="M24" s="3">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="N24" s="3">
         <v>5</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0D0F29-5D51-45DA-B0DB-1F083428078B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EA6F51-D9CE-49D6-A1FB-73040E1D5CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4455" yWindow="375" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="164">
   <si>
     <t>Name</t>
   </si>
@@ -3627,6 +3627,25 @@
         <family val="2"/>
       </rPr>
       <t>refabs/Enemy/Enemy_Prefab/Eclipse_Prefab</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dash</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>pread</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -4574,9 +4593,13 @@
       <c r="F6" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="13"/>
+      <c r="G6" s="13" t="s">
+        <v>162</v>
+      </c>
       <c r="H6" s="13"/>
-      <c r="I6" s="16"/>
+      <c r="I6" s="16">
+        <v>5</v>
+      </c>
       <c r="J6" s="14">
         <v>3</v>
       </c>
@@ -4593,7 +4616,9 @@
         <v>1</v>
       </c>
       <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
+      <c r="P6" s="14">
+        <v>2</v>
+      </c>
       <c r="Q6" s="14">
         <v>0.02</v>
       </c>
@@ -4739,7 +4764,7 @@
         <v>46</v>
       </c>
       <c r="I9" s="16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J9" s="14">
         <v>9</v>
@@ -4955,6 +4980,9 @@
       </c>
       <c r="F13" s="10" t="s">
         <v>44</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>163</v>
       </c>
       <c r="H13" s="14" t="s">
         <v>72</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36EA6F51-D9CE-49D6-A1FB-73040E1D5CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC9EDBD-E529-45B8-93F8-3EA6455A9180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="164">
   <si>
     <t>Name</t>
   </si>
@@ -4659,7 +4659,7 @@
         <v>7</v>
       </c>
       <c r="J7" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K7" s="14">
         <v>400</v>
@@ -4668,7 +4668,7 @@
         <v>3</v>
       </c>
       <c r="M7" s="14">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="N7" s="14">
         <v>4</v>
@@ -4711,7 +4711,7 @@
       <c r="H8" s="13"/>
       <c r="I8" s="16"/>
       <c r="J8" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K8" s="14">
         <v>600</v>
@@ -4776,7 +4776,7 @@
         <v>2</v>
       </c>
       <c r="M9" s="14">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="N9" s="14">
         <v>3</v>
@@ -4828,7 +4828,7 @@
         <v>3</v>
       </c>
       <c r="M10" s="14">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="N10" s="14">
         <v>4</v>
@@ -4871,7 +4871,7 @@
       <c r="H11" s="13"/>
       <c r="I11" s="16"/>
       <c r="J11" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K11" s="14">
         <v>2500</v>
@@ -4880,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="14">
-        <v>380</v>
+        <v>180</v>
       </c>
       <c r="N11" s="14">
         <v>5</v>
@@ -4929,7 +4929,7 @@
         <v>3</v>
       </c>
       <c r="J12" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K12" s="14">
         <v>4000</v>
@@ -4938,10 +4938,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="14">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="N12" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O12" s="14">
         <v>8</v>
@@ -4950,7 +4950,7 @@
         <v>2</v>
       </c>
       <c r="Q12" s="14">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="R12" s="14">
         <v>0.35</v>
@@ -4991,7 +4991,7 @@
         <v>7</v>
       </c>
       <c r="J13" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K13" s="3">
         <v>4000</v>
@@ -5000,13 +5000,13 @@
         <v>3</v>
       </c>
       <c r="M13" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N13" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q13" s="14">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="R13" s="14">
         <v>0.35</v>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="H14" s="14"/>
       <c r="J14" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K14" s="3">
         <v>7000</v>
@@ -5048,13 +5048,13 @@
         <v>1</v>
       </c>
       <c r="M14" s="3">
-        <v>250</v>
+        <v>480</v>
       </c>
       <c r="N14" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q14" s="14">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="R14" s="14">
         <v>0.35</v>
@@ -5086,7 +5086,7 @@
         <v>40</v>
       </c>
       <c r="J15" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K15" s="3">
         <v>12000</v>
@@ -5095,13 +5095,13 @@
         <v>5</v>
       </c>
       <c r="M15" s="3">
-        <v>800</v>
+        <v>680</v>
       </c>
       <c r="N15" s="3">
         <v>4</v>
       </c>
       <c r="Q15" s="14">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="R15" s="14">
         <v>0.4</v>
@@ -5139,7 +5139,7 @@
         <v>10</v>
       </c>
       <c r="J16" s="3">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K16" s="3">
         <v>9000</v>
@@ -5148,13 +5148,13 @@
         <v>3</v>
       </c>
       <c r="M16" s="3">
-        <v>1100</v>
+        <v>820</v>
       </c>
       <c r="N16" s="3">
         <v>5</v>
       </c>
       <c r="Q16" s="14">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="R16" s="14">
         <v>0.4</v>
@@ -5186,22 +5186,22 @@
         <v>40</v>
       </c>
       <c r="J17" s="3">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K17" s="3">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="L17" s="3">
         <v>1</v>
       </c>
       <c r="M17" s="3">
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="N17" s="3">
         <v>10</v>
       </c>
       <c r="Q17" s="14">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="R17" s="14">
         <v>0.4</v>
@@ -5233,7 +5233,7 @@
         <v>40</v>
       </c>
       <c r="J18" s="3">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K18" s="3">
         <v>7000</v>
@@ -5248,7 +5248,7 @@
         <v>2</v>
       </c>
       <c r="Q18" s="14">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="R18" s="14">
         <v>0.4</v>
@@ -5286,10 +5286,10 @@
         <v>92</v>
       </c>
       <c r="J19" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K19" s="3">
-        <v>17000</v>
+        <v>15000</v>
       </c>
       <c r="L19" s="3">
         <v>4</v>
@@ -5307,7 +5307,7 @@
         <v>3</v>
       </c>
       <c r="Q19" s="14">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="R19" s="14">
         <v>0.4</v>
@@ -5342,7 +5342,7 @@
         <v>97</v>
       </c>
       <c r="J20" s="3">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="K20" s="3">
         <v>7000</v>
@@ -5360,7 +5360,7 @@
         <v>1</v>
       </c>
       <c r="Q20" s="14">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="R20" s="14">
         <v>0.45</v>
@@ -5398,10 +5398,10 @@
         <v>110</v>
       </c>
       <c r="J21" s="3">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="K21" s="3">
-        <v>11000</v>
+        <v>16000</v>
       </c>
       <c r="L21" s="3">
         <v>2</v>
@@ -5419,7 +5419,7 @@
         <v>2.5</v>
       </c>
       <c r="Q21" s="14">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="R21" s="14">
         <v>0.45</v>
@@ -5457,10 +5457,10 @@
         <v>10</v>
       </c>
       <c r="J22" s="3">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="K22" s="3">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="L22" s="3">
         <v>4</v>
@@ -5475,7 +5475,7 @@
         <v>1.2</v>
       </c>
       <c r="Q22" s="14">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="R22" s="14">
         <v>0.45</v>
@@ -5507,7 +5507,7 @@
         <v>40</v>
       </c>
       <c r="J23" s="3">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="K23" s="3">
         <v>38000</v>
@@ -5522,7 +5522,7 @@
         <v>10</v>
       </c>
       <c r="Q23" s="14">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="R23" s="14">
         <v>0.45</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC9EDBD-E529-45B8-93F8-3EA6455A9180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6E1232-6052-4CD7-8E23-284497D7B34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="300" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -4668,7 +4668,7 @@
         <v>3</v>
       </c>
       <c r="M7" s="14">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="N7" s="14">
         <v>4</v>
@@ -4720,7 +4720,7 @@
         <v>4</v>
       </c>
       <c r="M8" s="14">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="N8" s="14">
         <v>2</v>
@@ -4770,13 +4770,13 @@
         <v>9</v>
       </c>
       <c r="K9" s="14">
-        <v>1200</v>
+        <v>2700</v>
       </c>
       <c r="L9" s="14">
         <v>2</v>
       </c>
       <c r="M9" s="14">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="N9" s="14">
         <v>3</v>
@@ -4790,7 +4790,7 @@
         <v>0.3</v>
       </c>
       <c r="S9" s="14">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="T9" s="14">
         <v>0.02</v>
@@ -4822,13 +4822,13 @@
         <v>9</v>
       </c>
       <c r="K10" s="14">
-        <v>900</v>
+        <v>2000</v>
       </c>
       <c r="L10" s="14">
         <v>3</v>
       </c>
       <c r="M10" s="14">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="N10" s="14">
         <v>4</v>
@@ -4842,7 +4842,7 @@
         <v>0.3</v>
       </c>
       <c r="S10" s="14">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="T10" s="14">
         <v>0.02</v>
@@ -4874,7 +4874,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="14">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="L11" s="14">
         <v>1</v>
@@ -4894,7 +4894,7 @@
         <v>0.3</v>
       </c>
       <c r="S11" s="14">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="T11" s="14">
         <v>0.02</v>
@@ -4932,13 +4932,13 @@
         <v>15</v>
       </c>
       <c r="K12" s="14">
-        <v>4000</v>
+        <v>5300</v>
       </c>
       <c r="L12" s="14">
         <v>2</v>
       </c>
       <c r="M12" s="14">
-        <v>350</v>
+        <v>475</v>
       </c>
       <c r="N12" s="14">
         <v>7</v>
@@ -4994,13 +4994,13 @@
         <v>15</v>
       </c>
       <c r="K13" s="3">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="L13" s="3">
         <v>3</v>
       </c>
       <c r="M13" s="3">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="N13" s="3">
         <v>5</v>
@@ -5042,13 +5042,13 @@
         <v>15</v>
       </c>
       <c r="K14" s="3">
-        <v>7000</v>
+        <v>7700</v>
       </c>
       <c r="L14" s="3">
         <v>1</v>
       </c>
       <c r="M14" s="3">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="N14" s="3">
         <v>3</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6E1232-6052-4CD7-8E23-284497D7B34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E40B2DF-E185-469A-99C4-1A6131736B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="300" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="0" windowWidth="27315" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -4662,7 +4662,7 @@
         <v>5</v>
       </c>
       <c r="K7" s="14">
-        <v>400</v>
+        <v>730</v>
       </c>
       <c r="L7" s="14">
         <v>3</v>
@@ -4714,7 +4714,7 @@
         <v>5</v>
       </c>
       <c r="K8" s="14">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="L8" s="14">
         <v>4</v>
@@ -4770,7 +4770,7 @@
         <v>9</v>
       </c>
       <c r="K9" s="14">
-        <v>2700</v>
+        <v>3200</v>
       </c>
       <c r="L9" s="14">
         <v>2</v>
@@ -4822,7 +4822,7 @@
         <v>9</v>
       </c>
       <c r="K10" s="14">
-        <v>2000</v>
+        <v>2900</v>
       </c>
       <c r="L10" s="14">
         <v>3</v>
@@ -4874,7 +4874,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="14">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="L11" s="14">
         <v>1</v>
@@ -4929,7 +4929,7 @@
         <v>3</v>
       </c>
       <c r="J12" s="14">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K12" s="14">
         <v>5300</v>
@@ -4941,7 +4941,7 @@
         <v>475</v>
       </c>
       <c r="N12" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O12" s="14">
         <v>8</v>
@@ -4991,19 +4991,19 @@
         <v>7</v>
       </c>
       <c r="J13" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K13" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="L13" s="3">
         <v>3</v>
       </c>
       <c r="M13" s="3">
-        <v>450</v>
+        <v>385</v>
       </c>
       <c r="N13" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q13" s="14">
         <v>0.05</v>
@@ -5039,10 +5039,10 @@
       </c>
       <c r="H14" s="14"/>
       <c r="J14" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K14" s="3">
-        <v>7700</v>
+        <v>6800</v>
       </c>
       <c r="L14" s="3">
         <v>1</v>
@@ -5086,7 +5086,7 @@
         <v>40</v>
       </c>
       <c r="J15" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K15" s="3">
         <v>12000</v>
@@ -5139,16 +5139,16 @@
         <v>10</v>
       </c>
       <c r="J16" s="3">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K16" s="3">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="L16" s="3">
         <v>3</v>
       </c>
       <c r="M16" s="3">
-        <v>820</v>
+        <v>740</v>
       </c>
       <c r="N16" s="3">
         <v>5</v>
@@ -5186,7 +5186,7 @@
         <v>40</v>
       </c>
       <c r="J17" s="3">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K17" s="3">
         <v>20000</v>
@@ -5195,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="N17" s="3">
         <v>10</v>
@@ -5233,16 +5233,16 @@
         <v>40</v>
       </c>
       <c r="J18" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K18" s="3">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="L18" s="3">
         <v>7</v>
       </c>
       <c r="M18" s="3">
-        <v>950</v>
+        <v>830</v>
       </c>
       <c r="N18" s="3">
         <v>2</v>
@@ -5286,7 +5286,7 @@
         <v>92</v>
       </c>
       <c r="J19" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K19" s="3">
         <v>15000</v>
@@ -5295,16 +5295,16 @@
         <v>4</v>
       </c>
       <c r="M19" s="3">
-        <v>1900</v>
+        <v>1200</v>
       </c>
       <c r="N19" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O19" s="3">
         <v>1</v>
       </c>
       <c r="P19" s="3">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q19" s="14">
         <v>0.1</v>
@@ -5342,7 +5342,7 @@
         <v>97</v>
       </c>
       <c r="J20" s="3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K20" s="3">
         <v>7000</v>
@@ -5351,7 +5351,7 @@
         <v>3</v>
       </c>
       <c r="M20" s="3">
-        <v>7000</v>
+        <v>5500</v>
       </c>
       <c r="N20" s="3">
         <v>1</v>
@@ -5507,7 +5507,7 @@
         <v>40</v>
       </c>
       <c r="J23" s="3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K23" s="3">
         <v>38000</v>
@@ -5564,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>3000000</v>
+        <v>10000000</v>
       </c>
       <c r="L24" s="3">
         <v>3</v>
@@ -5573,7 +5573,7 @@
         <v>8000</v>
       </c>
       <c r="N24" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>1</v>

--- a/JsonConverter/ExcelFiles/Enemy.xlsx
+++ b/JsonConverter/ExcelFiles/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E40B2DF-E185-469A-99C4-1A6131736B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FBCC14-147D-479F-BB6B-BCE251EF7E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="0" windowWidth="27315" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="0" windowWidth="27315" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -5564,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>10000000</v>
+        <v>100000</v>
       </c>
       <c r="L24" s="3">
         <v>3</v>
